--- a/DESPACHO_1.xlsx
+++ b/DESPACHO_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d104a1e6ce4108fd/Documentos/CLAUDE CODE DESPACHO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC520186-1EE4-423F-86CD-2FB04FF75A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{9C76EBBE-A3FD-47E7-B442-0B7A6A01484C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1F0266EB-9B6A-4235-B7BD-4818450586F7}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="118">
   <si>
     <t xml:space="preserve">PAN PAL DÍA </t>
   </si>
@@ -387,7 +387,10 @@
     <t>50+10+10</t>
   </si>
   <si>
-    <t>P03314</t>
+    <t>NE32</t>
+  </si>
+  <si>
+    <t>18678/P03314</t>
   </si>
 </sst>
 </file>
@@ -921,106 +924,114 @@
     <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1335,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E60A48-5AE1-4314-8AE1-760C8AA28F2B}">
-  <dimension ref="A1:S605"/>
+  <dimension ref="A1:S608"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" customWidth="1"/>
@@ -1371,16 +1382,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="111"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
@@ -1431,8 +1442,8 @@
       <c r="A4" s="12">
         <v>45879</v>
       </c>
-      <c r="B4" s="17">
-        <v>18678</v>
+      <c r="B4" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="C4">
         <v>200000</v>
@@ -1457,9 +1468,7 @@
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="B5" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="B5" s="17"/>
       <c r="D5">
         <v>12000</v>
       </c>
@@ -1509,7 +1518,7 @@
       <c r="F7" s="13">
         <v>46038</v>
       </c>
-      <c r="G7" s="137">
+      <c r="G7" s="102">
         <v>100000</v>
       </c>
       <c r="H7" s="15"/>
@@ -1518,14 +1527,10 @@
       <c r="K7"/>
     </row>
     <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="132"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="136"/>
+      <c r="A8" s="12"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="15"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1799,10 +1804,10 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="100" t="s">
+      <c r="E23" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="100"/>
+      <c r="F23" s="112"/>
       <c r="G23" s="27">
         <f>G7</f>
         <v>100000</v>
@@ -1818,16 +1823,16 @@
       <c r="K24"/>
     </row>
     <row r="25" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="123" t="s">
+      <c r="A25" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="124"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="124"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="125"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="115"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -1918,11 +1923,11 @@
       <c r="K29"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="112"/>
-      <c r="B30" s="111">
+      <c r="A30" s="116"/>
+      <c r="B30" s="117">
         <v>20724</v>
       </c>
-      <c r="C30" s="111">
+      <c r="C30" s="117">
         <v>380000</v>
       </c>
       <c r="D30">
@@ -1944,9 +1949,9 @@
       <c r="K30"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="112"/>
-      <c r="B31" s="111"/>
-      <c r="C31" s="111"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="117"/>
       <c r="D31">
         <v>9000</v>
       </c>
@@ -1966,9 +1971,9 @@
       <c r="K31"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="112"/>
-      <c r="B32" s="111"/>
-      <c r="C32" s="111"/>
+      <c r="A32" s="116"/>
+      <c r="B32" s="117"/>
+      <c r="C32" s="117"/>
       <c r="D32">
         <v>53100</v>
       </c>
@@ -1988,9 +1993,9 @@
       <c r="K32"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="112"/>
-      <c r="B33" s="111"/>
-      <c r="C33" s="111"/>
+      <c r="A33" s="116"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="117"/>
       <c r="D33">
         <v>20400</v>
       </c>
@@ -2010,9 +2015,9 @@
       <c r="K33"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="112"/>
-      <c r="B34" s="111"/>
-      <c r="C34" s="111"/>
+      <c r="A34" s="116"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="117"/>
       <c r="D34">
         <v>121200</v>
       </c>
@@ -2032,9 +2037,9 @@
       <c r="K34"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="112"/>
-      <c r="B35" s="111"/>
-      <c r="C35" s="111"/>
+      <c r="A35" s="116"/>
+      <c r="B35" s="117"/>
+      <c r="C35" s="117"/>
       <c r="D35">
         <f>27*1200</f>
         <v>32400</v>
@@ -2055,9 +2060,9 @@
       <c r="K35"/>
     </row>
     <row r="36" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="112"/>
-      <c r="B36" s="111"/>
-      <c r="C36" s="111"/>
+      <c r="A36" s="116"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="117"/>
       <c r="D36">
         <v>170000</v>
       </c>
@@ -2158,15 +2163,15 @@
       <c r="A41" s="24"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
-      <c r="D41" s="100" t="s">
+      <c r="D41" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="100"/>
-      <c r="F41" s="100"/>
-      <c r="G41" s="121">
+      <c r="E41" s="112"/>
+      <c r="F41" s="112"/>
+      <c r="G41" s="118">
         <v>0</v>
       </c>
-      <c r="H41" s="126"/>
+      <c r="H41" s="119"/>
       <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
@@ -2177,16 +2182,16 @@
       <c r="K42"/>
     </row>
     <row r="43" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="127" t="s">
+      <c r="A43" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="128"/>
-      <c r="C43" s="128"/>
-      <c r="D43" s="128"/>
-      <c r="E43" s="128"/>
-      <c r="F43" s="128"/>
-      <c r="G43" s="128"/>
-      <c r="H43" s="129"/>
+      <c r="B43" s="121"/>
+      <c r="C43" s="121"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="121"/>
+      <c r="H43" s="122"/>
       <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
@@ -2421,10 +2426,10 @@
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
-      <c r="E55" s="121" t="s">
+      <c r="E55" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="F55" s="121"/>
+      <c r="F55" s="118"/>
       <c r="G55" s="51">
         <v>0</v>
       </c>
@@ -2439,29 +2444,29 @@
       <c r="K56"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="101" t="s">
+      <c r="A57" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="102"/>
-      <c r="C57" s="102"/>
-      <c r="D57" s="102"/>
-      <c r="E57" s="102"/>
-      <c r="F57" s="102"/>
-      <c r="G57" s="102"/>
-      <c r="H57" s="103"/>
+      <c r="B57" s="110"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="110"/>
+      <c r="E57" s="110"/>
+      <c r="F57" s="110"/>
+      <c r="G57" s="110"/>
+      <c r="H57" s="111"/>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
     </row>
     <row r="58" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="104"/>
-      <c r="B58" s="105"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="E58" s="105"/>
-      <c r="F58" s="105"/>
-      <c r="G58" s="105"/>
-      <c r="H58" s="106"/>
+      <c r="A58" s="123"/>
+      <c r="B58" s="124"/>
+      <c r="C58" s="124"/>
+      <c r="D58" s="124"/>
+      <c r="E58" s="124"/>
+      <c r="F58" s="124"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="125"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
@@ -2569,15 +2574,15 @@
         <v>46224</v>
       </c>
       <c r="G63">
-        <f>C63-E63</f>
-        <v>108206</v>
+        <f>C63-D63</f>
+        <v>4000</v>
       </c>
       <c r="H63" s="35" t="s">
         <v>11</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
-      <c r="K63" s="130" t="s">
+      <c r="K63" s="100" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2599,10 +2604,10 @@
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
-      <c r="E65" s="122" t="s">
+      <c r="E65" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="F65" s="122"/>
+      <c r="F65" s="108"/>
       <c r="G65" s="27">
         <v>0</v>
       </c>
@@ -2617,16 +2622,16 @@
       <c r="K66"/>
     </row>
     <row r="67" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="123" t="s">
+      <c r="A67" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B67" s="124"/>
-      <c r="C67" s="124"/>
-      <c r="D67" s="124"/>
-      <c r="E67" s="124"/>
-      <c r="F67" s="124"/>
-      <c r="G67" s="124"/>
-      <c r="H67" s="125"/>
+      <c r="B67" s="114"/>
+      <c r="C67" s="114"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="114"/>
+      <c r="F67" s="114"/>
+      <c r="G67" s="114"/>
+      <c r="H67" s="115"/>
       <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
@@ -2789,10 +2794,10 @@
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
-      <c r="E75" s="100" t="s">
+      <c r="E75" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F75" s="100"/>
+      <c r="F75" s="112"/>
       <c r="G75" s="59">
         <v>0</v>
       </c>
@@ -2810,29 +2815,29 @@
       <c r="K76"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="101" t="s">
+      <c r="A77" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B77" s="102"/>
-      <c r="C77" s="102"/>
-      <c r="D77" s="102"/>
-      <c r="E77" s="102"/>
-      <c r="F77" s="102"/>
-      <c r="G77" s="102"/>
-      <c r="H77" s="103"/>
+      <c r="B77" s="110"/>
+      <c r="C77" s="110"/>
+      <c r="D77" s="110"/>
+      <c r="E77" s="110"/>
+      <c r="F77" s="110"/>
+      <c r="G77" s="110"/>
+      <c r="H77" s="111"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
     </row>
     <row r="78" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="104"/>
-      <c r="B78" s="105"/>
-      <c r="C78" s="105"/>
-      <c r="D78" s="105"/>
-      <c r="E78" s="105"/>
-      <c r="F78" s="105"/>
-      <c r="G78" s="105"/>
-      <c r="H78" s="106"/>
+      <c r="A78" s="123"/>
+      <c r="B78" s="124"/>
+      <c r="C78" s="124"/>
+      <c r="D78" s="124"/>
+      <c r="E78" s="124"/>
+      <c r="F78" s="124"/>
+      <c r="G78" s="124"/>
+      <c r="H78" s="125"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
@@ -2988,10 +2993,10 @@
       <c r="B86" s="25"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
-      <c r="E86" s="100" t="s">
+      <c r="E86" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F86" s="100"/>
+      <c r="F86" s="112"/>
       <c r="G86" s="59">
         <f>G84</f>
         <v>-21000</v>
@@ -3010,29 +3015,29 @@
       <c r="K87"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="101" t="s">
+      <c r="A88" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="B88" s="102"/>
-      <c r="C88" s="102"/>
-      <c r="D88" s="102"/>
-      <c r="E88" s="102"/>
-      <c r="F88" s="102"/>
-      <c r="G88" s="102"/>
-      <c r="H88" s="103"/>
+      <c r="B88" s="110"/>
+      <c r="C88" s="110"/>
+      <c r="D88" s="110"/>
+      <c r="E88" s="110"/>
+      <c r="F88" s="110"/>
+      <c r="G88" s="110"/>
+      <c r="H88" s="111"/>
       <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
     </row>
     <row r="89" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="104"/>
-      <c r="B89" s="105"/>
-      <c r="C89" s="105"/>
-      <c r="D89" s="105"/>
-      <c r="E89" s="105"/>
-      <c r="F89" s="105"/>
-      <c r="G89" s="105"/>
-      <c r="H89" s="106"/>
+      <c r="A89" s="123"/>
+      <c r="B89" s="124"/>
+      <c r="C89" s="124"/>
+      <c r="D89" s="124"/>
+      <c r="E89" s="124"/>
+      <c r="F89" s="124"/>
+      <c r="G89" s="124"/>
+      <c r="H89" s="125"/>
       <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
@@ -3067,14 +3072,14 @@
       <c r="K90"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="118"/>
-      <c r="B91" s="119"/>
-      <c r="C91" s="119"/>
-      <c r="D91" s="119"/>
-      <c r="E91" s="119"/>
-      <c r="F91" s="119"/>
-      <c r="G91" s="119"/>
-      <c r="H91" s="120"/>
+      <c r="A91" s="126"/>
+      <c r="B91" s="127"/>
+      <c r="C91" s="127"/>
+      <c r="D91" s="127"/>
+      <c r="E91" s="127"/>
+      <c r="F91" s="127"/>
+      <c r="G91" s="127"/>
+      <c r="H91" s="128"/>
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
@@ -3162,11 +3167,11 @@
       <c r="A96" s="24"/>
       <c r="B96" s="25"/>
       <c r="C96" s="25"/>
-      <c r="D96" s="100" t="s">
+      <c r="D96" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="E96" s="100"/>
-      <c r="F96" s="100"/>
+      <c r="E96" s="112"/>
+      <c r="F96" s="112"/>
       <c r="G96" s="70">
         <f>G94</f>
         <v>145000</v>
@@ -3182,29 +3187,29 @@
       <c r="K97"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" s="101" t="s">
+      <c r="A98" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="B98" s="102"/>
-      <c r="C98" s="102"/>
-      <c r="D98" s="102"/>
-      <c r="E98" s="102"/>
-      <c r="F98" s="102"/>
-      <c r="G98" s="102"/>
-      <c r="H98" s="103"/>
+      <c r="B98" s="110"/>
+      <c r="C98" s="110"/>
+      <c r="D98" s="110"/>
+      <c r="E98" s="110"/>
+      <c r="F98" s="110"/>
+      <c r="G98" s="110"/>
+      <c r="H98" s="111"/>
       <c r="I98"/>
       <c r="J98"/>
       <c r="K98"/>
     </row>
     <row r="99" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="104"/>
-      <c r="B99" s="105"/>
-      <c r="C99" s="105"/>
-      <c r="D99" s="105"/>
-      <c r="E99" s="105"/>
-      <c r="F99" s="105"/>
-      <c r="G99" s="105"/>
-      <c r="H99" s="106"/>
+      <c r="A99" s="123"/>
+      <c r="B99" s="124"/>
+      <c r="C99" s="124"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="124"/>
+      <c r="F99" s="124"/>
+      <c r="G99" s="124"/>
+      <c r="H99" s="125"/>
       <c r="I99"/>
       <c r="J99"/>
       <c r="K99"/>
@@ -3239,14 +3244,14 @@
       <c r="K100"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" s="115"/>
-      <c r="B101" s="116"/>
-      <c r="C101" s="116"/>
-      <c r="D101" s="116"/>
-      <c r="E101" s="116"/>
-      <c r="F101" s="116"/>
-      <c r="G101" s="116"/>
-      <c r="H101" s="117"/>
+      <c r="A101" s="129"/>
+      <c r="B101" s="130"/>
+      <c r="C101" s="130"/>
+      <c r="D101" s="130"/>
+      <c r="E101" s="130"/>
+      <c r="F101" s="130"/>
+      <c r="G101" s="130"/>
+      <c r="H101" s="131"/>
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
@@ -3370,10 +3375,10 @@
       <c r="B108" s="25"/>
       <c r="C108" s="25"/>
       <c r="D108" s="25"/>
-      <c r="E108" s="100" t="s">
+      <c r="E108" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F108" s="100"/>
+      <c r="F108" s="112"/>
       <c r="G108" s="70">
         <f>G104+G106</f>
         <v>200000</v>
@@ -3389,29 +3394,29 @@
       <c r="K109"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A110" s="101" t="s">
+      <c r="A110" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="B110" s="102"/>
-      <c r="C110" s="102"/>
-      <c r="D110" s="102"/>
-      <c r="E110" s="102"/>
-      <c r="F110" s="102"/>
-      <c r="G110" s="102"/>
-      <c r="H110" s="103"/>
+      <c r="B110" s="110"/>
+      <c r="C110" s="110"/>
+      <c r="D110" s="110"/>
+      <c r="E110" s="110"/>
+      <c r="F110" s="110"/>
+      <c r="G110" s="110"/>
+      <c r="H110" s="111"/>
       <c r="I110"/>
       <c r="J110"/>
       <c r="K110"/>
     </row>
     <row r="111" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="104"/>
-      <c r="B111" s="105"/>
-      <c r="C111" s="105"/>
-      <c r="D111" s="105"/>
-      <c r="E111" s="105"/>
-      <c r="F111" s="105"/>
-      <c r="G111" s="105"/>
-      <c r="H111" s="106"/>
+      <c r="A111" s="123"/>
+      <c r="B111" s="124"/>
+      <c r="C111" s="124"/>
+      <c r="D111" s="124"/>
+      <c r="E111" s="124"/>
+      <c r="F111" s="124"/>
+      <c r="G111" s="124"/>
+      <c r="H111" s="125"/>
       <c r="I111"/>
       <c r="J111"/>
       <c r="K111"/>
@@ -3522,7 +3527,7 @@
         <f>C116-D116</f>
         <v>-4000</v>
       </c>
-      <c r="H116" s="131" t="s">
+      <c r="H116" s="101" t="s">
         <v>11</v>
       </c>
       <c r="I116"/>
@@ -3547,10 +3552,10 @@
       <c r="B118" s="25"/>
       <c r="C118" s="25"/>
       <c r="D118" s="25"/>
-      <c r="E118" s="100" t="s">
+      <c r="E118" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F118" s="100"/>
+      <c r="F118" s="112"/>
       <c r="G118" s="70">
         <v>0</v>
       </c>
@@ -3565,29 +3570,29 @@
       <c r="K119"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="101" t="s">
+      <c r="A120" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="B120" s="102"/>
-      <c r="C120" s="102"/>
-      <c r="D120" s="102"/>
-      <c r="E120" s="102"/>
-      <c r="F120" s="102"/>
-      <c r="G120" s="102"/>
-      <c r="H120" s="103"/>
+      <c r="B120" s="110"/>
+      <c r="C120" s="110"/>
+      <c r="D120" s="110"/>
+      <c r="E120" s="110"/>
+      <c r="F120" s="110"/>
+      <c r="G120" s="110"/>
+      <c r="H120" s="111"/>
       <c r="I120"/>
       <c r="J120"/>
       <c r="K120"/>
     </row>
     <row r="121" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="104"/>
-      <c r="B121" s="105"/>
-      <c r="C121" s="105"/>
-      <c r="D121" s="105"/>
-      <c r="E121" s="105"/>
-      <c r="F121" s="105"/>
-      <c r="G121" s="105"/>
-      <c r="H121" s="106"/>
+      <c r="A121" s="123"/>
+      <c r="B121" s="124"/>
+      <c r="C121" s="124"/>
+      <c r="D121" s="124"/>
+      <c r="E121" s="124"/>
+      <c r="F121" s="124"/>
+      <c r="G121" s="124"/>
+      <c r="H121" s="125"/>
       <c r="I121"/>
       <c r="J121"/>
       <c r="K121"/>
@@ -3788,10 +3793,10 @@
       <c r="B131" s="58"/>
       <c r="C131" s="58"/>
       <c r="D131" s="58"/>
-      <c r="E131" s="114" t="s">
+      <c r="E131" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="F131" s="114"/>
+      <c r="F131" s="132"/>
       <c r="G131" s="84">
         <f>G125+G129</f>
         <v>106000</v>
@@ -3807,29 +3812,29 @@
       <c r="K132"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A133" s="101" t="s">
+      <c r="A133" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="B133" s="102"/>
-      <c r="C133" s="102"/>
-      <c r="D133" s="102"/>
-      <c r="E133" s="102"/>
-      <c r="F133" s="102"/>
-      <c r="G133" s="102"/>
-      <c r="H133" s="103"/>
+      <c r="B133" s="110"/>
+      <c r="C133" s="110"/>
+      <c r="D133" s="110"/>
+      <c r="E133" s="110"/>
+      <c r="F133" s="110"/>
+      <c r="G133" s="110"/>
+      <c r="H133" s="111"/>
       <c r="I133"/>
       <c r="J133"/>
       <c r="K133"/>
     </row>
     <row r="134" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="104"/>
-      <c r="B134" s="105"/>
-      <c r="C134" s="105"/>
-      <c r="D134" s="105"/>
-      <c r="E134" s="105"/>
-      <c r="F134" s="105"/>
-      <c r="G134" s="105"/>
-      <c r="H134" s="106"/>
+      <c r="A134" s="123"/>
+      <c r="B134" s="124"/>
+      <c r="C134" s="124"/>
+      <c r="D134" s="124"/>
+      <c r="E134" s="124"/>
+      <c r="F134" s="124"/>
+      <c r="G134" s="124"/>
+      <c r="H134" s="125"/>
       <c r="I134"/>
       <c r="J134"/>
       <c r="K134"/>
@@ -4036,10 +4041,10 @@
       <c r="B144" s="25"/>
       <c r="C144" s="25"/>
       <c r="D144" s="25"/>
-      <c r="E144" s="100" t="s">
+      <c r="E144" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F144" s="100"/>
+      <c r="F144" s="112"/>
       <c r="G144" s="70">
         <v>0</v>
       </c>
@@ -4054,29 +4059,29 @@
       <c r="K145"/>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A146" s="101" t="s">
+      <c r="A146" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="B146" s="102"/>
-      <c r="C146" s="102"/>
-      <c r="D146" s="102"/>
-      <c r="E146" s="102"/>
-      <c r="F146" s="102"/>
-      <c r="G146" s="102"/>
-      <c r="H146" s="103"/>
+      <c r="B146" s="110"/>
+      <c r="C146" s="110"/>
+      <c r="D146" s="110"/>
+      <c r="E146" s="110"/>
+      <c r="F146" s="110"/>
+      <c r="G146" s="110"/>
+      <c r="H146" s="111"/>
       <c r="I146"/>
       <c r="J146"/>
       <c r="K146"/>
     </row>
     <row r="147" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="104"/>
-      <c r="B147" s="105"/>
-      <c r="C147" s="105"/>
-      <c r="D147" s="105"/>
-      <c r="E147" s="105"/>
-      <c r="F147" s="105"/>
-      <c r="G147" s="105"/>
-      <c r="H147" s="106"/>
+      <c r="A147" s="123"/>
+      <c r="B147" s="124"/>
+      <c r="C147" s="124"/>
+      <c r="D147" s="124"/>
+      <c r="E147" s="124"/>
+      <c r="F147" s="124"/>
+      <c r="G147" s="124"/>
+      <c r="H147" s="125"/>
       <c r="I147"/>
       <c r="J147"/>
       <c r="K147"/>
@@ -4199,29 +4204,29 @@
       <c r="K153"/>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A154" s="101" t="s">
+      <c r="A154" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="B154" s="102"/>
-      <c r="C154" s="102"/>
-      <c r="D154" s="102"/>
-      <c r="E154" s="102"/>
-      <c r="F154" s="102"/>
-      <c r="G154" s="102"/>
-      <c r="H154" s="103"/>
+      <c r="B154" s="110"/>
+      <c r="C154" s="110"/>
+      <c r="D154" s="110"/>
+      <c r="E154" s="110"/>
+      <c r="F154" s="110"/>
+      <c r="G154" s="110"/>
+      <c r="H154" s="111"/>
       <c r="I154"/>
       <c r="J154"/>
       <c r="K154"/>
     </row>
     <row r="155" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="104"/>
-      <c r="B155" s="105"/>
-      <c r="C155" s="105"/>
-      <c r="D155" s="105"/>
-      <c r="E155" s="105"/>
-      <c r="F155" s="105"/>
-      <c r="G155" s="105"/>
-      <c r="H155" s="106"/>
+      <c r="A155" s="123"/>
+      <c r="B155" s="124"/>
+      <c r="C155" s="124"/>
+      <c r="D155" s="124"/>
+      <c r="E155" s="124"/>
+      <c r="F155" s="124"/>
+      <c r="G155" s="124"/>
+      <c r="H155" s="125"/>
       <c r="I155"/>
       <c r="J155"/>
       <c r="K155"/>
@@ -4323,10 +4328,10 @@
       <c r="B160" s="25"/>
       <c r="C160" s="25"/>
       <c r="D160" s="25"/>
-      <c r="E160" s="100" t="s">
+      <c r="E160" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F160" s="100"/>
+      <c r="F160" s="112"/>
       <c r="G160" s="70">
         <v>0</v>
       </c>
@@ -4346,29 +4351,29 @@
       <c r="K161"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A162" s="101" t="s">
+      <c r="A162" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="B162" s="102"/>
-      <c r="C162" s="102"/>
-      <c r="D162" s="102"/>
-      <c r="E162" s="102"/>
-      <c r="F162" s="102"/>
-      <c r="G162" s="102"/>
-      <c r="H162" s="103"/>
+      <c r="B162" s="110"/>
+      <c r="C162" s="110"/>
+      <c r="D162" s="110"/>
+      <c r="E162" s="110"/>
+      <c r="F162" s="110"/>
+      <c r="G162" s="110"/>
+      <c r="H162" s="111"/>
       <c r="I162"/>
       <c r="J162"/>
       <c r="K162"/>
     </row>
     <row r="163" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="104"/>
-      <c r="B163" s="105"/>
-      <c r="C163" s="105"/>
-      <c r="D163" s="105"/>
-      <c r="E163" s="105"/>
-      <c r="F163" s="105"/>
-      <c r="G163" s="105"/>
-      <c r="H163" s="106"/>
+      <c r="A163" s="123"/>
+      <c r="B163" s="124"/>
+      <c r="C163" s="124"/>
+      <c r="D163" s="124"/>
+      <c r="E163" s="124"/>
+      <c r="F163" s="124"/>
+      <c r="G163" s="124"/>
+      <c r="H163" s="125"/>
       <c r="I163"/>
       <c r="J163"/>
       <c r="K163"/>
@@ -4505,29 +4510,29 @@
       <c r="K170"/>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A171" s="101" t="s">
+      <c r="A171" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="B171" s="102"/>
-      <c r="C171" s="102"/>
-      <c r="D171" s="102"/>
-      <c r="E171" s="102"/>
-      <c r="F171" s="102"/>
-      <c r="G171" s="102"/>
-      <c r="H171" s="103"/>
+      <c r="B171" s="110"/>
+      <c r="C171" s="110"/>
+      <c r="D171" s="110"/>
+      <c r="E171" s="110"/>
+      <c r="F171" s="110"/>
+      <c r="G171" s="110"/>
+      <c r="H171" s="111"/>
       <c r="I171"/>
       <c r="J171"/>
       <c r="K171"/>
     </row>
     <row r="172" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="104"/>
-      <c r="B172" s="105"/>
-      <c r="C172" s="105"/>
-      <c r="D172" s="105"/>
-      <c r="E172" s="105"/>
-      <c r="F172" s="105"/>
-      <c r="G172" s="105"/>
-      <c r="H172" s="106"/>
+      <c r="A172" s="123"/>
+      <c r="B172" s="124"/>
+      <c r="C172" s="124"/>
+      <c r="D172" s="124"/>
+      <c r="E172" s="124"/>
+      <c r="F172" s="124"/>
+      <c r="G172" s="124"/>
+      <c r="H172" s="125"/>
       <c r="I172"/>
       <c r="J172"/>
       <c r="K172"/>
@@ -4604,10 +4609,10 @@
       <c r="B176" s="25"/>
       <c r="C176" s="25"/>
       <c r="D176" s="25"/>
-      <c r="E176" s="100" t="s">
+      <c r="E176" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F176" s="100"/>
+      <c r="F176" s="112"/>
       <c r="G176" s="70">
         <v>0</v>
       </c>
@@ -4622,29 +4627,29 @@
       <c r="K177"/>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A178" s="101" t="s">
+      <c r="A178" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="B178" s="102"/>
-      <c r="C178" s="102"/>
-      <c r="D178" s="102"/>
-      <c r="E178" s="102"/>
-      <c r="F178" s="102"/>
-      <c r="G178" s="102"/>
-      <c r="H178" s="103"/>
+      <c r="B178" s="110"/>
+      <c r="C178" s="110"/>
+      <c r="D178" s="110"/>
+      <c r="E178" s="110"/>
+      <c r="F178" s="110"/>
+      <c r="G178" s="110"/>
+      <c r="H178" s="111"/>
       <c r="I178"/>
       <c r="J178"/>
       <c r="K178"/>
     </row>
     <row r="179" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="104"/>
-      <c r="B179" s="105"/>
-      <c r="C179" s="105"/>
-      <c r="D179" s="105"/>
-      <c r="E179" s="105"/>
-      <c r="F179" s="105"/>
-      <c r="G179" s="105"/>
-      <c r="H179" s="106"/>
+      <c r="A179" s="123"/>
+      <c r="B179" s="124"/>
+      <c r="C179" s="124"/>
+      <c r="D179" s="124"/>
+      <c r="E179" s="124"/>
+      <c r="F179" s="124"/>
+      <c r="G179" s="124"/>
+      <c r="H179" s="125"/>
       <c r="I179"/>
       <c r="J179"/>
       <c r="K179"/>
@@ -4721,10 +4726,10 @@
       <c r="B183" s="25"/>
       <c r="C183" s="25"/>
       <c r="D183" s="25"/>
-      <c r="E183" s="100" t="s">
+      <c r="E183" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F183" s="100"/>
+      <c r="F183" s="112"/>
       <c r="G183" s="70">
         <v>0</v>
       </c>
@@ -4739,29 +4744,29 @@
       <c r="K184"/>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A185" s="101" t="s">
+      <c r="A185" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="B185" s="102"/>
-      <c r="C185" s="102"/>
-      <c r="D185" s="102"/>
-      <c r="E185" s="102"/>
-      <c r="F185" s="102"/>
-      <c r="G185" s="102"/>
-      <c r="H185" s="103"/>
+      <c r="B185" s="110"/>
+      <c r="C185" s="110"/>
+      <c r="D185" s="110"/>
+      <c r="E185" s="110"/>
+      <c r="F185" s="110"/>
+      <c r="G185" s="110"/>
+      <c r="H185" s="111"/>
       <c r="I185"/>
       <c r="J185"/>
       <c r="K185"/>
     </row>
     <row r="186" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="104"/>
-      <c r="B186" s="105"/>
-      <c r="C186" s="105"/>
-      <c r="D186" s="105"/>
-      <c r="E186" s="105"/>
-      <c r="F186" s="105"/>
-      <c r="G186" s="105"/>
-      <c r="H186" s="106"/>
+      <c r="A186" s="123"/>
+      <c r="B186" s="124"/>
+      <c r="C186" s="124"/>
+      <c r="D186" s="124"/>
+      <c r="E186" s="124"/>
+      <c r="F186" s="124"/>
+      <c r="G186" s="124"/>
+      <c r="H186" s="125"/>
       <c r="I186"/>
       <c r="J186"/>
       <c r="K186"/>
@@ -4868,10 +4873,10 @@
       <c r="B192" s="25"/>
       <c r="C192" s="25"/>
       <c r="D192" s="25"/>
-      <c r="E192" s="100" t="s">
+      <c r="E192" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F192" s="100"/>
+      <c r="F192" s="112"/>
       <c r="G192" s="70">
         <v>5300</v>
       </c>
@@ -4888,29 +4893,29 @@
       <c r="K193"/>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A194" s="101" t="s">
+      <c r="A194" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="B194" s="102"/>
-      <c r="C194" s="102"/>
-      <c r="D194" s="102"/>
-      <c r="E194" s="102"/>
-      <c r="F194" s="102"/>
-      <c r="G194" s="102"/>
-      <c r="H194" s="103"/>
+      <c r="B194" s="110"/>
+      <c r="C194" s="110"/>
+      <c r="D194" s="110"/>
+      <c r="E194" s="110"/>
+      <c r="F194" s="110"/>
+      <c r="G194" s="110"/>
+      <c r="H194" s="111"/>
       <c r="I194"/>
       <c r="J194"/>
       <c r="K194"/>
     </row>
     <row r="195" spans="1:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="104"/>
-      <c r="B195" s="105"/>
-      <c r="C195" s="105"/>
-      <c r="D195" s="105"/>
-      <c r="E195" s="105"/>
-      <c r="F195" s="105"/>
-      <c r="G195" s="105"/>
-      <c r="H195" s="106"/>
+      <c r="A195" s="123"/>
+      <c r="B195" s="124"/>
+      <c r="C195" s="124"/>
+      <c r="D195" s="124"/>
+      <c r="E195" s="124"/>
+      <c r="F195" s="124"/>
+      <c r="G195" s="124"/>
+      <c r="H195" s="125"/>
       <c r="I195"/>
       <c r="J195"/>
       <c r="K195"/>
@@ -5173,10 +5178,10 @@
       <c r="B208" s="25"/>
       <c r="C208" s="25"/>
       <c r="D208" s="25"/>
-      <c r="E208" s="100" t="s">
+      <c r="E208" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F208" s="100"/>
+      <c r="F208" s="112"/>
       <c r="G208" s="70">
         <f>G204+G206</f>
         <v>33000</v>
@@ -5192,29 +5197,29 @@
       <c r="K209"/>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A210" s="101" t="s">
+      <c r="A210" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="B210" s="102"/>
-      <c r="C210" s="102"/>
-      <c r="D210" s="102"/>
-      <c r="E210" s="102"/>
-      <c r="F210" s="102"/>
-      <c r="G210" s="102"/>
-      <c r="H210" s="103"/>
+      <c r="B210" s="110"/>
+      <c r="C210" s="110"/>
+      <c r="D210" s="110"/>
+      <c r="E210" s="110"/>
+      <c r="F210" s="110"/>
+      <c r="G210" s="110"/>
+      <c r="H210" s="111"/>
       <c r="I210"/>
       <c r="J210"/>
       <c r="K210"/>
     </row>
     <row r="211" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="104"/>
-      <c r="B211" s="105"/>
-      <c r="C211" s="105"/>
-      <c r="D211" s="105"/>
-      <c r="E211" s="105"/>
-      <c r="F211" s="105"/>
-      <c r="G211" s="105"/>
-      <c r="H211" s="106"/>
+      <c r="A211" s="123"/>
+      <c r="B211" s="124"/>
+      <c r="C211" s="124"/>
+      <c r="D211" s="124"/>
+      <c r="E211" s="124"/>
+      <c r="F211" s="124"/>
+      <c r="G211" s="124"/>
+      <c r="H211" s="125"/>
       <c r="I211"/>
       <c r="J211"/>
       <c r="K211"/>
@@ -5248,359 +5253,362 @@
       <c r="J212"/>
       <c r="K212"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A213" s="40"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="5"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="5"/>
-      <c r="H213" s="8"/>
+    <row r="213" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A213" s="34">
+        <v>45863</v>
+      </c>
+      <c r="B213" s="19">
+        <v>18501</v>
+      </c>
+      <c r="C213">
+        <v>50000</v>
+      </c>
+      <c r="D213" s="19">
+        <v>12000</v>
+      </c>
+      <c r="E213" s="106">
+        <v>41342</v>
+      </c>
+      <c r="F213" s="81">
+        <v>45890</v>
+      </c>
+      <c r="G213" s="19">
+        <f>C213-D213</f>
+        <v>38000</v>
+      </c>
+      <c r="H213" s="105"/>
       <c r="I213"/>
       <c r="J213"/>
       <c r="K213"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A214" s="112">
-        <v>46126</v>
-      </c>
-      <c r="B214" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="C214" s="113">
-        <v>50000</v>
-      </c>
-      <c r="D214">
-        <v>10000</v>
-      </c>
-      <c r="E214">
-        <v>41694</v>
-      </c>
-      <c r="F214" s="13">
-        <v>46148</v>
-      </c>
-      <c r="G214">
-        <f>C214-D214</f>
-        <v>40000</v>
-      </c>
-      <c r="H214" s="15"/>
+    <row r="214" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A214" s="34"/>
+      <c r="B214" s="19"/>
+      <c r="D214" s="19">
+        <v>6600</v>
+      </c>
+      <c r="E214" s="106" t="s">
+        <v>116</v>
+      </c>
+      <c r="F214" s="81">
+        <v>45908</v>
+      </c>
+      <c r="G214" s="19">
+        <f>G213-D214</f>
+        <v>31400</v>
+      </c>
+      <c r="H214" s="107" t="s">
+        <v>46</v>
+      </c>
       <c r="I214"/>
       <c r="J214"/>
       <c r="K214"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A215" s="110"/>
-      <c r="B215" s="111"/>
-      <c r="C215" s="113"/>
-      <c r="D215">
-        <v>20000</v>
-      </c>
-      <c r="E215">
-        <v>41696</v>
-      </c>
-      <c r="F215" s="13">
-        <v>46150</v>
-      </c>
-      <c r="G215">
-        <f>G214-D215</f>
-        <v>20000</v>
-      </c>
-      <c r="H215" s="15"/>
+    <row r="215" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A215" s="103"/>
+      <c r="B215" s="104"/>
+      <c r="C215" s="104"/>
+      <c r="D215" s="104"/>
+      <c r="E215" s="104"/>
+      <c r="F215" s="104"/>
+      <c r="G215" s="104"/>
+      <c r="H215" s="105"/>
       <c r="I215"/>
       <c r="J215"/>
       <c r="K215"/>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A216" s="110"/>
-      <c r="B216" s="111"/>
-      <c r="C216" s="113"/>
-      <c r="D216">
-        <v>19000</v>
-      </c>
-      <c r="E216">
-        <v>41729</v>
-      </c>
-      <c r="F216" s="13">
-        <v>46177</v>
-      </c>
-      <c r="G216">
-        <f>G215-D216</f>
-        <v>1000</v>
-      </c>
-      <c r="H216" s="15" t="s">
-        <v>11</v>
-      </c>
+      <c r="A216" s="40"/>
+      <c r="B216" s="5"/>
+      <c r="C216" s="5"/>
+      <c r="D216" s="5"/>
+      <c r="E216" s="5"/>
+      <c r="F216" s="6"/>
+      <c r="G216" s="5"/>
+      <c r="H216" s="8"/>
       <c r="I216"/>
       <c r="J216"/>
       <c r="K216"/>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A217" s="71"/>
-      <c r="B217" s="41"/>
-      <c r="C217" s="5"/>
-      <c r="D217" s="5"/>
-      <c r="E217" s="5"/>
-      <c r="F217" s="6"/>
-      <c r="G217" s="5"/>
-      <c r="H217" s="8"/>
+      <c r="A217" s="116">
+        <v>46126</v>
+      </c>
+      <c r="B217" s="117" t="s">
+        <v>66</v>
+      </c>
+      <c r="C217" s="134">
+        <v>50000</v>
+      </c>
+      <c r="D217">
+        <v>10000</v>
+      </c>
+      <c r="E217">
+        <v>41694</v>
+      </c>
+      <c r="F217" s="13">
+        <v>46148</v>
+      </c>
+      <c r="G217">
+        <f>C217-D217</f>
+        <v>40000</v>
+      </c>
+      <c r="H217" s="15"/>
       <c r="I217"/>
       <c r="J217"/>
       <c r="K217"/>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A218" s="39">
-        <v>46149</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C218">
-        <v>50000</v>
-      </c>
-      <c r="F218" s="13"/>
+      <c r="A218" s="133"/>
+      <c r="B218" s="117"/>
+      <c r="C218" s="134"/>
+      <c r="D218">
+        <v>20000</v>
+      </c>
+      <c r="E218">
+        <v>41696</v>
+      </c>
+      <c r="F218" s="13">
+        <v>46150</v>
+      </c>
       <c r="G218">
-        <f>C218-D218</f>
-        <v>50000</v>
-      </c>
-      <c r="H218" s="22" t="s">
-        <v>41</v>
-      </c>
+        <f>G217-D218</f>
+        <v>20000</v>
+      </c>
+      <c r="H218" s="15"/>
       <c r="I218"/>
       <c r="J218"/>
       <c r="K218"/>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A219" s="87"/>
-      <c r="B219" s="41"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
-      <c r="E219" s="5"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="5"/>
-      <c r="H219" s="88"/>
+      <c r="A219" s="133"/>
+      <c r="B219" s="117"/>
+      <c r="C219" s="134"/>
+      <c r="D219">
+        <v>19000</v>
+      </c>
+      <c r="E219">
+        <v>41729</v>
+      </c>
+      <c r="F219" s="13">
+        <v>46177</v>
+      </c>
+      <c r="G219">
+        <f>G218-D219</f>
+        <v>1000</v>
+      </c>
+      <c r="H219" s="15" t="s">
+        <v>11</v>
+      </c>
       <c r="I219"/>
       <c r="J219"/>
       <c r="K219"/>
     </row>
-    <row r="220" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="24"/>
-      <c r="B220" s="25"/>
-      <c r="C220" s="25"/>
-      <c r="D220" s="25"/>
-      <c r="E220" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="F220" s="100"/>
-      <c r="G220" s="70">
-        <f>G218</f>
-        <v>50000</v>
-      </c>
-      <c r="H220" s="28"/>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A220" s="71"/>
+      <c r="B220" s="41"/>
+      <c r="C220" s="5"/>
+      <c r="D220" s="5"/>
+      <c r="E220" s="5"/>
+      <c r="F220" s="6"/>
+      <c r="G220" s="5"/>
+      <c r="H220" s="8"/>
       <c r="I220"/>
       <c r="J220"/>
       <c r="K220"/>
     </row>
-    <row r="221" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A221" s="39">
+        <v>46149</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C221">
+        <v>50000</v>
+      </c>
+      <c r="F221" s="13"/>
+      <c r="G221">
+        <f>C221-D221</f>
+        <v>50000</v>
+      </c>
+      <c r="H221" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I221"/>
       <c r="J221"/>
       <c r="K221"/>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A222" s="101" t="s">
-        <v>68</v>
-      </c>
-      <c r="B222" s="102"/>
-      <c r="C222" s="102"/>
-      <c r="D222" s="102"/>
-      <c r="E222" s="102"/>
-      <c r="F222" s="102"/>
-      <c r="G222" s="102"/>
-      <c r="H222" s="103"/>
+      <c r="A222" s="87"/>
+      <c r="B222" s="41"/>
+      <c r="C222" s="5"/>
+      <c r="D222" s="5"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="6"/>
+      <c r="G222" s="5"/>
+      <c r="H222" s="88"/>
       <c r="I222"/>
       <c r="J222"/>
       <c r="K222"/>
     </row>
-    <row r="223" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="104"/>
-      <c r="B223" s="105"/>
-      <c r="C223" s="105"/>
-      <c r="D223" s="105"/>
-      <c r="E223" s="105"/>
-      <c r="F223" s="105"/>
-      <c r="G223" s="105"/>
-      <c r="H223" s="106"/>
+    <row r="223" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="24"/>
+      <c r="B223" s="25"/>
+      <c r="C223" s="25"/>
+      <c r="D223" s="25"/>
+      <c r="E223" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F223" s="112"/>
+      <c r="G223" s="70">
+        <f>G221+G214</f>
+        <v>81400</v>
+      </c>
+      <c r="H223" s="28"/>
       <c r="I223"/>
       <c r="J223"/>
       <c r="K223"/>
     </row>
-    <row r="224" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B224" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C224" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E224" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F224" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G224" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="H224" s="31" t="s">
-        <v>8</v>
-      </c>
+    <row r="224" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I224"/>
       <c r="J224"/>
       <c r="K224"/>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A225" s="4"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="33"/>
-      <c r="D225" s="5"/>
-      <c r="E225" s="89"/>
-      <c r="F225" s="6"/>
-      <c r="G225" s="5"/>
-      <c r="H225" s="8"/>
+      <c r="A225" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="B225" s="110"/>
+      <c r="C225" s="110"/>
+      <c r="D225" s="110"/>
+      <c r="E225" s="110"/>
+      <c r="F225" s="110"/>
+      <c r="G225" s="110"/>
+      <c r="H225" s="111"/>
       <c r="I225"/>
       <c r="J225"/>
       <c r="K225"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A226" s="12">
-        <v>46318</v>
-      </c>
-      <c r="B226">
-        <v>19408</v>
-      </c>
-      <c r="C226" s="19">
-        <v>400000</v>
-      </c>
-      <c r="D226">
-        <v>38100</v>
-      </c>
-      <c r="E226" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="F226" s="13">
-        <v>46057</v>
-      </c>
-      <c r="G226">
-        <f>C226-D226</f>
-        <v>361900</v>
-      </c>
-      <c r="H226" s="15"/>
+    <row r="226" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="123"/>
+      <c r="B226" s="124"/>
+      <c r="C226" s="124"/>
+      <c r="D226" s="124"/>
+      <c r="E226" s="124"/>
+      <c r="F226" s="124"/>
+      <c r="G226" s="124"/>
+      <c r="H226" s="125"/>
       <c r="I226"/>
       <c r="J226"/>
       <c r="K226"/>
     </row>
-    <row r="227" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="12"/>
-      <c r="C227" s="19"/>
-      <c r="D227">
-        <v>40000</v>
-      </c>
-      <c r="E227" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F227" s="13">
-        <v>46098</v>
-      </c>
-      <c r="G227">
-        <f t="shared" ref="G227:G232" si="1">G226-D227</f>
-        <v>321900</v>
-      </c>
-      <c r="H227" s="15"/>
+    <row r="227" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B227" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C227" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E227" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F227" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G227" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H227" s="31" t="s">
+        <v>8</v>
+      </c>
       <c r="I227"/>
       <c r="J227"/>
       <c r="K227"/>
     </row>
-    <row r="228" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="12"/>
-      <c r="C228" s="19"/>
-      <c r="D228">
-        <v>41000</v>
-      </c>
-      <c r="E228" t="s">
-        <v>71</v>
-      </c>
-      <c r="F228" s="13">
-        <v>46108</v>
-      </c>
-      <c r="G228">
-        <f t="shared" si="1"/>
-        <v>280900</v>
-      </c>
-      <c r="H228" s="15"/>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A228" s="4"/>
+      <c r="B228" s="5"/>
+      <c r="C228" s="33"/>
+      <c r="D228" s="5"/>
+      <c r="E228" s="89"/>
+      <c r="F228" s="6"/>
+      <c r="G228" s="5"/>
+      <c r="H228" s="8"/>
       <c r="I228"/>
       <c r="J228"/>
       <c r="K228"/>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A229" s="12"/>
-      <c r="C229" s="19"/>
+      <c r="A229" s="12">
+        <v>46318</v>
+      </c>
+      <c r="B229">
+        <v>19408</v>
+      </c>
+      <c r="C229" s="19">
+        <v>400000</v>
+      </c>
       <c r="D229">
-        <v>52000</v>
+        <v>38100</v>
       </c>
       <c r="E229" s="21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F229" s="13">
-        <v>46126</v>
+        <v>46057</v>
       </c>
       <c r="G229">
-        <f t="shared" si="1"/>
-        <v>228900</v>
-      </c>
+        <f>C229-D229</f>
+        <v>361900</v>
+      </c>
+      <c r="H229" s="15"/>
       <c r="I229"/>
       <c r="J229"/>
       <c r="K229"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12"/>
       <c r="C230" s="19"/>
       <c r="D230">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F230" s="13">
-        <v>46210</v>
+        <v>46098</v>
       </c>
       <c r="G230">
-        <f t="shared" si="1"/>
-        <v>216900</v>
-      </c>
+        <f t="shared" ref="G230:G235" si="1">G229-D230</f>
+        <v>321900</v>
+      </c>
+      <c r="H230" s="15"/>
       <c r="I230"/>
       <c r="J230"/>
       <c r="K230"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="12"/>
       <c r="C231" s="19"/>
       <c r="D231">
-        <v>39000</v>
-      </c>
-      <c r="E231" s="21" t="s">
-        <v>74</v>
+        <v>41000</v>
+      </c>
+      <c r="E231" t="s">
+        <v>71</v>
       </c>
       <c r="F231" s="13">
-        <v>46212</v>
+        <v>46108</v>
       </c>
       <c r="G231">
         <f t="shared" si="1"/>
-        <v>177900</v>
+        <v>280900</v>
       </c>
       <c r="H231" s="15"/>
       <c r="I231"/>
@@ -5611,664 +5619,662 @@
       <c r="A232" s="12"/>
       <c r="C232" s="19"/>
       <c r="D232">
-        <v>54000</v>
-      </c>
-      <c r="E232" s="21">
-        <v>41780</v>
+        <v>52000</v>
+      </c>
+      <c r="E232" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="F232" s="13">
-        <v>46219</v>
+        <v>46126</v>
       </c>
       <c r="G232">
         <f t="shared" si="1"/>
-        <v>123900</v>
-      </c>
-      <c r="H232" s="15" t="s">
-        <v>62</v>
+        <v>228900</v>
       </c>
       <c r="I232"/>
       <c r="J232"/>
       <c r="K232"/>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A233" s="40"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="5"/>
-      <c r="F233" s="6"/>
-      <c r="G233" s="5"/>
-      <c r="H233" s="8"/>
+      <c r="A233" s="12"/>
+      <c r="C233" s="19"/>
+      <c r="D233">
+        <v>12000</v>
+      </c>
+      <c r="E233" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F233" s="13">
+        <v>46210</v>
+      </c>
+      <c r="G233">
+        <f t="shared" si="1"/>
+        <v>216900</v>
+      </c>
       <c r="I233"/>
       <c r="J233"/>
       <c r="K233"/>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A234" s="12">
-        <v>46126</v>
-      </c>
-      <c r="B234" t="s">
-        <v>75</v>
-      </c>
-      <c r="C234">
-        <v>50000</v>
-      </c>
+      <c r="A234" s="12"/>
+      <c r="C234" s="19"/>
       <c r="D234">
-        <v>20000</v>
-      </c>
-      <c r="E234" s="90">
-        <v>41728</v>
+        <v>39000</v>
+      </c>
+      <c r="E234" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="F234" s="13">
-        <v>46177</v>
-      </c>
+        <v>46212</v>
+      </c>
+      <c r="G234">
+        <f t="shared" si="1"/>
+        <v>177900</v>
+      </c>
+      <c r="H234" s="15"/>
       <c r="I234"/>
       <c r="J234"/>
       <c r="K234"/>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="12"/>
+      <c r="C235" s="19"/>
       <c r="D235">
-        <v>10000</v>
-      </c>
-      <c r="E235">
-        <v>41756</v>
+        <v>54000</v>
+      </c>
+      <c r="E235" s="21">
+        <v>41780</v>
       </c>
       <c r="F235" s="13">
-        <v>46204</v>
-      </c>
-      <c r="H235" s="15"/>
+        <v>46219</v>
+      </c>
+      <c r="G235">
+        <f t="shared" si="1"/>
+        <v>123900</v>
+      </c>
+      <c r="H235" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="I235"/>
       <c r="J235"/>
       <c r="K235"/>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A236" s="12"/>
-      <c r="D236">
-        <v>12000</v>
-      </c>
-      <c r="E236">
-        <v>41760</v>
-      </c>
-      <c r="F236" s="13">
-        <v>46205</v>
-      </c>
-      <c r="H236" s="15"/>
+      <c r="A236" s="40"/>
+      <c r="B236" s="5"/>
+      <c r="C236" s="5"/>
+      <c r="D236" s="5"/>
+      <c r="E236" s="5"/>
+      <c r="F236" s="6"/>
+      <c r="G236" s="5"/>
+      <c r="H236" s="8"/>
       <c r="I236"/>
       <c r="J236"/>
       <c r="K236"/>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A237" s="12"/>
+      <c r="A237" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B237" t="s">
+        <v>75</v>
+      </c>
+      <c r="C237">
+        <v>50000</v>
+      </c>
       <c r="D237">
-        <v>10000</v>
-      </c>
-      <c r="E237">
-        <v>41761</v>
+        <v>20000</v>
+      </c>
+      <c r="E237" s="90">
+        <v>41728</v>
       </c>
       <c r="F237" s="13">
-        <v>46206</v>
-      </c>
-      <c r="G237">
-        <v>0</v>
-      </c>
-      <c r="H237" s="15" t="s">
-        <v>29</v>
+        <v>46177</v>
       </c>
       <c r="I237"/>
       <c r="J237"/>
       <c r="K237"/>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A238" s="4"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
-      <c r="E238" s="5"/>
-      <c r="F238" s="6"/>
-      <c r="G238" s="5"/>
-      <c r="H238" s="8"/>
+      <c r="A238" s="12"/>
+      <c r="D238">
+        <v>10000</v>
+      </c>
+      <c r="E238">
+        <v>41756</v>
+      </c>
+      <c r="F238" s="13">
+        <v>46204</v>
+      </c>
+      <c r="H238" s="15"/>
       <c r="I238"/>
       <c r="J238"/>
       <c r="K238"/>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A239" s="12">
-        <v>46149</v>
-      </c>
-      <c r="B239" t="s">
-        <v>76</v>
-      </c>
-      <c r="C239">
-        <v>170000</v>
-      </c>
-      <c r="F239" s="13"/>
-      <c r="G239">
-        <f>C239-D239</f>
-        <v>170000</v>
-      </c>
-      <c r="H239" s="22" t="s">
-        <v>46</v>
-      </c>
+      <c r="A239" s="12"/>
+      <c r="D239">
+        <v>12000</v>
+      </c>
+      <c r="E239">
+        <v>41760</v>
+      </c>
+      <c r="F239" s="13">
+        <v>46205</v>
+      </c>
+      <c r="H239" s="15"/>
       <c r="I239"/>
       <c r="J239"/>
       <c r="K239"/>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A240" s="40"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5"/>
-      <c r="D240" s="5"/>
-      <c r="E240" s="5"/>
-      <c r="F240" s="6"/>
-      <c r="G240" s="5"/>
-      <c r="H240" s="8"/>
+      <c r="A240" s="12"/>
+      <c r="D240">
+        <v>10000</v>
+      </c>
+      <c r="E240">
+        <v>41761</v>
+      </c>
+      <c r="F240" s="13">
+        <v>46206</v>
+      </c>
+      <c r="G240">
+        <v>0</v>
+      </c>
+      <c r="H240" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="I240"/>
       <c r="J240"/>
       <c r="K240"/>
     </row>
-    <row r="241" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="24"/>
-      <c r="B241" s="25"/>
-      <c r="C241" s="25"/>
-      <c r="D241" s="25"/>
-      <c r="E241" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="F241" s="100"/>
-      <c r="G241" s="70">
-        <f>G231+G239</f>
-        <v>347900</v>
-      </c>
-      <c r="H241" s="28"/>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A241" s="4"/>
+      <c r="B241" s="5"/>
+      <c r="C241" s="5"/>
+      <c r="D241" s="5"/>
+      <c r="E241" s="5"/>
+      <c r="F241" s="6"/>
+      <c r="G241" s="5"/>
+      <c r="H241" s="8"/>
       <c r="I241"/>
       <c r="J241"/>
       <c r="K241"/>
     </row>
-    <row r="242" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A242" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B242" t="s">
+        <v>76</v>
+      </c>
+      <c r="C242">
+        <v>170000</v>
+      </c>
+      <c r="F242" s="13"/>
+      <c r="G242">
+        <f>C242-D242</f>
+        <v>170000</v>
+      </c>
+      <c r="H242" s="22" t="s">
+        <v>46</v>
+      </c>
       <c r="I242"/>
       <c r="J242"/>
       <c r="K242"/>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A243" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="B243" s="102"/>
-      <c r="C243" s="102"/>
-      <c r="D243" s="102"/>
-      <c r="E243" s="102"/>
-      <c r="F243" s="102"/>
-      <c r="G243" s="102"/>
-      <c r="H243" s="103"/>
+      <c r="A243" s="40"/>
+      <c r="B243" s="5"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5"/>
+      <c r="E243" s="5"/>
+      <c r="F243" s="6"/>
+      <c r="G243" s="5"/>
+      <c r="H243" s="8"/>
       <c r="I243"/>
       <c r="J243"/>
       <c r="K243"/>
     </row>
-    <row r="244" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="104"/>
-      <c r="B244" s="105"/>
-      <c r="C244" s="105"/>
-      <c r="D244" s="105"/>
-      <c r="E244" s="105"/>
-      <c r="F244" s="105"/>
-      <c r="G244" s="105"/>
-      <c r="H244" s="106"/>
+    <row r="244" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="24"/>
+      <c r="B244" s="25"/>
+      <c r="C244" s="25"/>
+      <c r="D244" s="25"/>
+      <c r="E244" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F244" s="112"/>
+      <c r="G244" s="70">
+        <f>G234+G242</f>
+        <v>347900</v>
+      </c>
+      <c r="H244" s="28"/>
       <c r="I244"/>
       <c r="J244"/>
       <c r="K244"/>
     </row>
-    <row r="245" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B245" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C245" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D245" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E245" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F245" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G245" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="H245" s="31" t="s">
-        <v>8</v>
-      </c>
+    <row r="245" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I245"/>
       <c r="J245"/>
       <c r="K245"/>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A246" s="40"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
-      <c r="D246" s="5"/>
-      <c r="E246" s="5"/>
-      <c r="F246" s="6"/>
-      <c r="G246" s="5"/>
-      <c r="H246" s="8"/>
+      <c r="A246" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="B246" s="110"/>
+      <c r="C246" s="110"/>
+      <c r="D246" s="110"/>
+      <c r="E246" s="110"/>
+      <c r="F246" s="110"/>
+      <c r="G246" s="110"/>
+      <c r="H246" s="111"/>
       <c r="I246"/>
       <c r="J246"/>
       <c r="K246"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A247" s="12">
-        <v>46126</v>
-      </c>
-      <c r="B247">
-        <v>20725</v>
-      </c>
-      <c r="C247">
-        <v>100000</v>
-      </c>
-      <c r="D247">
-        <v>31500</v>
-      </c>
-      <c r="E247" t="s">
-        <v>78</v>
-      </c>
-      <c r="F247" s="13">
-        <v>46126</v>
-      </c>
-      <c r="G247">
-        <f>C247-D247</f>
-        <v>68500</v>
-      </c>
+    <row r="247" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="123"/>
+      <c r="B247" s="124"/>
+      <c r="C247" s="124"/>
+      <c r="D247" s="124"/>
+      <c r="E247" s="124"/>
+      <c r="F247" s="124"/>
+      <c r="G247" s="124"/>
+      <c r="H247" s="125"/>
       <c r="I247"/>
       <c r="J247"/>
       <c r="K247"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A248" s="43"/>
-      <c r="D248">
-        <v>45000</v>
-      </c>
-      <c r="E248" s="90">
-        <v>41735</v>
-      </c>
-      <c r="F248" s="13">
-        <v>46181</v>
-      </c>
-      <c r="G248">
-        <f>G247-D248</f>
-        <v>23500</v>
-      </c>
-      <c r="H248" s="15"/>
+    <row r="248" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B248" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C248" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E248" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F248" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G248" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H248" s="31" t="s">
+        <v>8</v>
+      </c>
       <c r="I248"/>
       <c r="J248"/>
       <c r="K248"/>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A249" s="43"/>
-      <c r="D249">
-        <v>21100</v>
-      </c>
-      <c r="E249" s="90">
-        <v>41740</v>
-      </c>
-      <c r="F249" s="13">
-        <v>46184</v>
-      </c>
-      <c r="G249">
-        <f>G248-D249</f>
-        <v>2400</v>
-      </c>
-      <c r="H249" s="15" t="s">
-        <v>11</v>
-      </c>
+      <c r="A249" s="40"/>
+      <c r="B249" s="5"/>
+      <c r="C249" s="5"/>
+      <c r="D249" s="5"/>
+      <c r="E249" s="5"/>
+      <c r="F249" s="6"/>
+      <c r="G249" s="5"/>
+      <c r="H249" s="8"/>
       <c r="I249"/>
       <c r="J249"/>
       <c r="K249"/>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A250" s="40"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="5"/>
-      <c r="D250" s="5"/>
-      <c r="E250" s="5"/>
-      <c r="F250" s="6"/>
-      <c r="G250" s="5"/>
-      <c r="H250" s="8"/>
+      <c r="A250" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B250">
+        <v>20725</v>
+      </c>
+      <c r="C250">
+        <v>100000</v>
+      </c>
+      <c r="D250">
+        <v>31500</v>
+      </c>
+      <c r="E250" t="s">
+        <v>78</v>
+      </c>
+      <c r="F250" s="13">
+        <v>46126</v>
+      </c>
+      <c r="G250">
+        <f>C250-D250</f>
+        <v>68500</v>
+      </c>
       <c r="I250"/>
       <c r="J250"/>
       <c r="K250"/>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A251" s="12">
-        <v>46126</v>
-      </c>
-      <c r="B251" t="s">
-        <v>79</v>
-      </c>
-      <c r="C251">
-        <v>75000</v>
-      </c>
-      <c r="F251" s="13"/>
+      <c r="A251" s="43"/>
+      <c r="D251">
+        <v>45000</v>
+      </c>
+      <c r="E251" s="90">
+        <v>41735</v>
+      </c>
+      <c r="F251" s="13">
+        <v>46181</v>
+      </c>
       <c r="G251">
-        <f>C251</f>
-        <v>75000</v>
-      </c>
-      <c r="H251" s="15" t="s">
-        <v>62</v>
-      </c>
+        <f>G250-D251</f>
+        <v>23500</v>
+      </c>
+      <c r="H251" s="15"/>
       <c r="I251"/>
       <c r="J251"/>
       <c r="K251"/>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A252" s="40"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5"/>
-      <c r="D252" s="5"/>
-      <c r="E252" s="5"/>
-      <c r="F252" s="6"/>
-      <c r="G252" s="5"/>
-      <c r="H252" s="8"/>
+      <c r="A252" s="43"/>
+      <c r="D252">
+        <v>21100</v>
+      </c>
+      <c r="E252" s="90">
+        <v>41740</v>
+      </c>
+      <c r="F252" s="13">
+        <v>46184</v>
+      </c>
+      <c r="G252">
+        <f>G251-D252</f>
+        <v>2400</v>
+      </c>
+      <c r="H252" s="15" t="s">
+        <v>11</v>
+      </c>
       <c r="I252"/>
       <c r="J252"/>
       <c r="K252"/>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A253" s="12">
-        <v>46149</v>
-      </c>
-      <c r="B253" t="s">
-        <v>80</v>
-      </c>
-      <c r="C253">
-        <v>70000</v>
-      </c>
-      <c r="F253" s="13"/>
-      <c r="G253">
-        <v>70000</v>
-      </c>
-      <c r="H253" s="22" t="s">
-        <v>41</v>
-      </c>
+      <c r="A253" s="40"/>
+      <c r="B253" s="5"/>
+      <c r="C253" s="5"/>
+      <c r="D253" s="5"/>
+      <c r="E253" s="5"/>
+      <c r="F253" s="6"/>
+      <c r="G253" s="5"/>
+      <c r="H253" s="8"/>
       <c r="I253"/>
       <c r="J253"/>
       <c r="K253"/>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A254" s="40"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
-      <c r="E254" s="5"/>
-      <c r="F254" s="6"/>
-      <c r="G254" s="5"/>
-      <c r="H254" s="8"/>
+      <c r="A254" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B254" t="s">
+        <v>79</v>
+      </c>
+      <c r="C254">
+        <v>75000</v>
+      </c>
+      <c r="F254" s="13"/>
+      <c r="G254">
+        <f>C254</f>
+        <v>75000</v>
+      </c>
+      <c r="H254" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="I254"/>
       <c r="J254"/>
       <c r="K254"/>
     </row>
-    <row r="255" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="24"/>
-      <c r="B255" s="25"/>
-      <c r="C255" s="25"/>
-      <c r="D255" s="25"/>
-      <c r="E255" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="F255" s="100"/>
-      <c r="G255" s="70">
-        <f>G251+G253</f>
-        <v>145000</v>
-      </c>
-      <c r="H255" s="28"/>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A255" s="40"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="5"/>
+      <c r="D255" s="5"/>
+      <c r="E255" s="5"/>
+      <c r="F255" s="6"/>
+      <c r="G255" s="5"/>
+      <c r="H255" s="8"/>
       <c r="I255"/>
       <c r="J255"/>
       <c r="K255"/>
     </row>
-    <row r="256" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A256" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B256" t="s">
+        <v>80</v>
+      </c>
+      <c r="C256">
+        <v>70000</v>
+      </c>
+      <c r="F256" s="13"/>
+      <c r="G256">
+        <v>70000</v>
+      </c>
+      <c r="H256" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I256"/>
       <c r="J256"/>
       <c r="K256"/>
     </row>
-    <row r="257" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="101" t="s">
-        <v>81</v>
-      </c>
-      <c r="B257" s="102"/>
-      <c r="C257" s="102"/>
-      <c r="D257" s="102"/>
-      <c r="E257" s="102"/>
-      <c r="F257" s="102"/>
-      <c r="G257" s="102"/>
-      <c r="H257" s="103"/>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A257" s="40"/>
+      <c r="B257" s="5"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="6"/>
+      <c r="G257" s="5"/>
+      <c r="H257" s="8"/>
       <c r="I257"/>
       <c r="J257"/>
       <c r="K257"/>
     </row>
-    <row r="258" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="104"/>
-      <c r="B258" s="105"/>
-      <c r="C258" s="105"/>
-      <c r="D258" s="105"/>
-      <c r="E258" s="105"/>
-      <c r="F258" s="105"/>
-      <c r="G258" s="105"/>
-      <c r="H258" s="106"/>
+    <row r="258" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A258" s="24"/>
+      <c r="B258" s="25"/>
+      <c r="C258" s="25"/>
+      <c r="D258" s="25"/>
+      <c r="E258" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F258" s="112"/>
+      <c r="G258" s="70">
+        <f>G254+G256</f>
+        <v>145000</v>
+      </c>
+      <c r="H258" s="28"/>
       <c r="I258"/>
       <c r="J258"/>
       <c r="K258"/>
     </row>
-    <row r="259" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E259" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F259" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G259" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H259" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="259" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I259"/>
       <c r="J259"/>
       <c r="K259"/>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A260" s="37"/>
-      <c r="B260" s="33"/>
-      <c r="C260" s="33"/>
-      <c r="D260" s="5"/>
-      <c r="E260" s="89"/>
-      <c r="F260" s="6"/>
-      <c r="G260" s="5"/>
-      <c r="H260" s="8"/>
+    <row r="260" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="109" t="s">
+        <v>81</v>
+      </c>
+      <c r="B260" s="110"/>
+      <c r="C260" s="110"/>
+      <c r="D260" s="110"/>
+      <c r="E260" s="110"/>
+      <c r="F260" s="110"/>
+      <c r="G260" s="110"/>
+      <c r="H260" s="111"/>
       <c r="I260"/>
       <c r="J260"/>
       <c r="K260"/>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A261" s="34">
-        <v>46126</v>
-      </c>
-      <c r="B261" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C261" s="19">
-        <v>290000</v>
-      </c>
-      <c r="D261">
-        <v>23000</v>
-      </c>
-      <c r="E261" s="21">
-        <v>41710</v>
-      </c>
-      <c r="F261" s="13">
-        <v>46156</v>
-      </c>
-      <c r="G261">
-        <f>C261-D261</f>
-        <v>267000</v>
-      </c>
-      <c r="H261" s="15"/>
+    <row r="261" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A261" s="123"/>
+      <c r="B261" s="124"/>
+      <c r="C261" s="124"/>
+      <c r="D261" s="124"/>
+      <c r="E261" s="124"/>
+      <c r="F261" s="124"/>
+      <c r="G261" s="124"/>
+      <c r="H261" s="125"/>
       <c r="I261"/>
       <c r="J261"/>
       <c r="K261"/>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A262" s="34"/>
-      <c r="B262" s="19"/>
-      <c r="C262" s="19"/>
-      <c r="D262">
-        <v>65000</v>
-      </c>
-      <c r="E262" s="21">
-        <v>41733</v>
-      </c>
-      <c r="F262" s="13">
-        <v>46177</v>
-      </c>
-      <c r="G262">
-        <f>G261-D262</f>
-        <v>202000</v>
-      </c>
-      <c r="H262" s="15"/>
+    <row r="262" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A262" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I262"/>
       <c r="J262"/>
       <c r="K262"/>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A263" s="34"/>
-      <c r="B263" s="19"/>
-      <c r="C263" s="19"/>
-      <c r="D263">
-        <v>28000</v>
-      </c>
-      <c r="E263" s="21">
-        <v>41734</v>
-      </c>
-      <c r="F263" s="13">
-        <v>46181</v>
-      </c>
-      <c r="G263">
-        <f>G262-D263</f>
-        <v>174000</v>
-      </c>
-      <c r="H263" s="15"/>
+      <c r="A263" s="37"/>
+      <c r="B263" s="33"/>
+      <c r="C263" s="33"/>
+      <c r="D263" s="5"/>
+      <c r="E263" s="89"/>
+      <c r="F263" s="6"/>
+      <c r="G263" s="5"/>
+      <c r="H263" s="8"/>
       <c r="I263"/>
       <c r="J263"/>
       <c r="K263"/>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A264" s="34"/>
-      <c r="B264" s="19"/>
-      <c r="C264" s="19"/>
+      <c r="A264" s="34">
+        <v>46126</v>
+      </c>
+      <c r="B264" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C264" s="19">
+        <v>290000</v>
+      </c>
       <c r="D264">
-        <v>174000</v>
+        <v>23000</v>
       </c>
       <c r="E264" s="21">
-        <v>41739</v>
+        <v>41710</v>
       </c>
       <c r="F264" s="13">
-        <v>46184</v>
+        <v>46156</v>
       </c>
       <c r="G264">
-        <f>G263-D264</f>
-        <v>0</v>
-      </c>
-      <c r="H264" s="15" t="s">
-        <v>11</v>
-      </c>
+        <f>C264-D264</f>
+        <v>267000</v>
+      </c>
+      <c r="H264" s="15"/>
       <c r="I264"/>
       <c r="J264"/>
       <c r="K264"/>
     </row>
-    <row r="265" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="37"/>
-      <c r="B265" s="33"/>
-      <c r="C265" s="33"/>
-      <c r="D265" s="5"/>
-      <c r="E265" s="89"/>
-      <c r="F265" s="6"/>
-      <c r="G265" s="5"/>
-      <c r="H265" s="8"/>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A265" s="34"/>
+      <c r="B265" s="19"/>
+      <c r="C265" s="19"/>
+      <c r="D265">
+        <v>65000</v>
+      </c>
+      <c r="E265" s="21">
+        <v>41733</v>
+      </c>
+      <c r="F265" s="13">
+        <v>46177</v>
+      </c>
+      <c r="G265">
+        <f>G264-D265</f>
+        <v>202000</v>
+      </c>
+      <c r="H265" s="15"/>
       <c r="I265"/>
       <c r="J265"/>
       <c r="K265"/>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A266" s="12">
-        <v>46149</v>
-      </c>
-      <c r="B266" t="s">
-        <v>83</v>
-      </c>
-      <c r="C266">
-        <v>140000</v>
-      </c>
+      <c r="A266" s="34"/>
+      <c r="B266" s="19"/>
+      <c r="C266" s="19"/>
       <c r="D266">
-        <v>87000</v>
+        <v>28000</v>
       </c>
       <c r="E266" s="21">
-        <v>41759</v>
+        <v>41734</v>
       </c>
       <c r="F266" s="13">
-        <v>46205</v>
+        <v>46181</v>
       </c>
       <c r="G266">
-        <f>C266-D266</f>
-        <v>53000</v>
-      </c>
-      <c r="H266" s="22" t="s">
-        <v>11</v>
-      </c>
+        <f>G265-D266</f>
+        <v>174000</v>
+      </c>
+      <c r="H266" s="15"/>
       <c r="I266"/>
       <c r="J266"/>
       <c r="K266"/>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A267" s="43"/>
+      <c r="A267" s="34"/>
+      <c r="B267" s="19"/>
+      <c r="C267" s="19"/>
       <c r="D267">
-        <v>65000</v>
+        <v>174000</v>
       </c>
       <c r="E267" s="21">
-        <v>41765</v>
+        <v>41739</v>
       </c>
       <c r="F267" s="13">
-        <v>46210</v>
+        <v>46184</v>
       </c>
       <c r="G267">
         <f>G266-D267</f>
-        <v>-12000</v>
-      </c>
-      <c r="H267" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="H267" s="15" t="s">
+        <v>11</v>
+      </c>
       <c r="I267"/>
       <c r="J267"/>
       <c r="K267"/>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A268" s="40"/>
-      <c r="B268" s="5"/>
-      <c r="C268" s="5"/>
+    <row r="268" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="37"/>
+      <c r="B268" s="33"/>
+      <c r="C268" s="33"/>
       <c r="D268" s="5"/>
-      <c r="E268" s="5"/>
+      <c r="E268" s="89"/>
       <c r="F268" s="6"/>
       <c r="G268" s="5"/>
       <c r="H268" s="8"/>
@@ -6276,180 +6282,192 @@
       <c r="J268"/>
       <c r="K268"/>
     </row>
-    <row r="269" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="24"/>
-      <c r="B269" s="25"/>
-      <c r="C269" s="25"/>
-      <c r="D269" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="E269" s="100"/>
-      <c r="F269" s="100"/>
-      <c r="G269" s="70">
-        <v>0</v>
-      </c>
-      <c r="H269" s="28"/>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A269" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B269" t="s">
+        <v>83</v>
+      </c>
+      <c r="C269">
+        <v>140000</v>
+      </c>
+      <c r="D269">
+        <v>87000</v>
+      </c>
+      <c r="E269" s="21">
+        <v>41759</v>
+      </c>
+      <c r="F269" s="13">
+        <v>46205</v>
+      </c>
+      <c r="G269">
+        <f>C269-D269</f>
+        <v>53000</v>
+      </c>
+      <c r="H269" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="I269"/>
       <c r="J269"/>
       <c r="K269"/>
     </row>
-    <row r="270" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A270" s="43"/>
+      <c r="D270">
+        <v>65000</v>
+      </c>
+      <c r="E270" s="21">
+        <v>41765</v>
+      </c>
+      <c r="F270" s="13">
+        <v>46210</v>
+      </c>
+      <c r="G270">
+        <f>G269-D270</f>
+        <v>-12000</v>
+      </c>
+      <c r="H270" s="15"/>
       <c r="I270"/>
       <c r="J270"/>
       <c r="K270"/>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A271" s="101" t="s">
-        <v>84</v>
-      </c>
-      <c r="B271" s="102"/>
-      <c r="C271" s="102"/>
-      <c r="D271" s="102"/>
-      <c r="E271" s="102"/>
-      <c r="F271" s="102"/>
-      <c r="G271" s="102"/>
-      <c r="H271" s="103"/>
+      <c r="A271" s="40"/>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5"/>
+      <c r="D271" s="5"/>
+      <c r="E271" s="5"/>
+      <c r="F271" s="6"/>
+      <c r="G271" s="5"/>
+      <c r="H271" s="8"/>
       <c r="I271"/>
       <c r="J271"/>
       <c r="K271"/>
     </row>
-    <row r="272" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="107"/>
-      <c r="B272" s="108"/>
-      <c r="C272" s="108"/>
-      <c r="D272" s="108"/>
-      <c r="E272" s="108"/>
-      <c r="F272" s="108"/>
-      <c r="G272" s="108"/>
-      <c r="H272" s="109"/>
+    <row r="272" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="24"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+      <c r="D272" s="112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E272" s="112"/>
+      <c r="F272" s="112"/>
+      <c r="G272" s="70">
+        <v>0</v>
+      </c>
+      <c r="H272" s="28"/>
       <c r="I272"/>
       <c r="J272"/>
       <c r="K272"/>
     </row>
-    <row r="273" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E273" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F273" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H273" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="273" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I273"/>
       <c r="J273"/>
       <c r="K273"/>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A274" s="91">
-        <v>45975</v>
-      </c>
-      <c r="B274" s="92">
-        <v>19850</v>
-      </c>
-      <c r="C274" s="92">
-        <v>2000</v>
-      </c>
-      <c r="D274">
-        <v>2000</v>
-      </c>
-      <c r="E274" t="s">
-        <v>85</v>
-      </c>
-      <c r="F274" s="13">
-        <v>45995</v>
-      </c>
-      <c r="G274">
-        <f>C274-D274</f>
-        <v>0</v>
-      </c>
-      <c r="H274" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="A274" s="109" t="s">
+        <v>84</v>
+      </c>
+      <c r="B274" s="110"/>
+      <c r="C274" s="110"/>
+      <c r="D274" s="110"/>
+      <c r="E274" s="110"/>
+      <c r="F274" s="110"/>
+      <c r="G274" s="110"/>
+      <c r="H274" s="111"/>
       <c r="I274"/>
       <c r="J274"/>
       <c r="K274"/>
     </row>
-    <row r="275" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="12"/>
-      <c r="F275" s="13"/>
-      <c r="H275" s="15"/>
+    <row r="275" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="135"/>
+      <c r="B275" s="136"/>
+      <c r="C275" s="136"/>
+      <c r="D275" s="136"/>
+      <c r="E275" s="136"/>
+      <c r="F275" s="136"/>
+      <c r="G275" s="136"/>
+      <c r="H275" s="137"/>
       <c r="I275"/>
       <c r="J275"/>
       <c r="K275"/>
     </row>
-    <row r="276" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="32"/>
-      <c r="B276" s="33"/>
-      <c r="C276" s="33"/>
-      <c r="D276" s="5"/>
-      <c r="E276" s="5"/>
-      <c r="F276" s="6"/>
-      <c r="G276" s="5"/>
-      <c r="H276" s="8"/>
+    <row r="276" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A276" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G276" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H276" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I276"/>
       <c r="J276"/>
       <c r="K276"/>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A277" s="34">
+      <c r="A277" s="91">
         <v>45975</v>
       </c>
-      <c r="B277" s="19">
-        <v>19851</v>
-      </c>
-      <c r="C277" s="19">
+      <c r="B277" s="92">
+        <v>19850</v>
+      </c>
+      <c r="C277" s="92">
         <v>2000</v>
       </c>
       <c r="D277">
         <v>2000</v>
       </c>
-      <c r="E277" s="21" t="s">
-        <v>86</v>
+      <c r="E277" t="s">
+        <v>85</v>
       </c>
       <c r="F277" s="13">
-        <v>46386</v>
+        <v>45995</v>
       </c>
       <c r="G277">
         <f>C277-D277</f>
         <v>0</v>
       </c>
-      <c r="H277" s="15"/>
+      <c r="H277" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="I277"/>
       <c r="J277"/>
       <c r="K277"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A278" s="34"/>
-      <c r="B278" s="19"/>
-      <c r="C278" s="19"/>
-      <c r="E278" s="21"/>
+    <row r="278" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="12"/>
       <c r="F278" s="13"/>
+      <c r="H278" s="15"/>
       <c r="I278"/>
       <c r="J278"/>
       <c r="K278"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A279" s="37"/>
+    <row r="279" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="32"/>
       <c r="B279" s="33"/>
       <c r="C279" s="33"/>
       <c r="D279" s="5"/>
-      <c r="E279" s="89"/>
+      <c r="E279" s="5"/>
       <c r="F279" s="6"/>
       <c r="G279" s="5"/>
       <c r="H279" s="8"/>
@@ -6462,23 +6480,23 @@
         <v>45975</v>
       </c>
       <c r="B280" s="19">
-        <v>19997</v>
+        <v>19851</v>
       </c>
       <c r="C280" s="19">
         <v>2000</v>
       </c>
       <c r="D280">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F280" s="13">
-        <v>45995</v>
+        <v>46386</v>
       </c>
       <c r="G280">
         <f>C280-D280</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H280" s="15"/>
       <c r="I280"/>
@@ -6489,22 +6507,8 @@
       <c r="A281" s="34"/>
       <c r="B281" s="19"/>
       <c r="C281" s="19"/>
-      <c r="D281">
-        <v>800</v>
-      </c>
-      <c r="E281" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F281" s="13">
-        <v>46001</v>
-      </c>
-      <c r="G281">
-        <f>G280-D281</f>
-        <v>0</v>
-      </c>
-      <c r="H281" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="E281" s="21"/>
+      <c r="F281" s="13"/>
       <c r="I281"/>
       <c r="J281"/>
       <c r="K281"/>
@@ -6523,100 +6527,105 @@
       <c r="K282"/>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A283" s="40"/>
-      <c r="B283" s="5"/>
-      <c r="C283" s="5"/>
-      <c r="D283" s="5"/>
-      <c r="E283" s="5"/>
-      <c r="F283" s="6"/>
-      <c r="G283" s="5"/>
-      <c r="H283" s="8"/>
+      <c r="A283" s="34">
+        <v>45975</v>
+      </c>
+      <c r="B283" s="19">
+        <v>19997</v>
+      </c>
+      <c r="C283" s="19">
+        <v>2000</v>
+      </c>
+      <c r="D283">
+        <v>1200</v>
+      </c>
+      <c r="E283" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F283" s="13">
+        <v>45995</v>
+      </c>
+      <c r="G283">
+        <f>C283-D283</f>
+        <v>800</v>
+      </c>
+      <c r="H283" s="15"/>
       <c r="I283"/>
       <c r="J283"/>
       <c r="K283"/>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A284" s="93" t="s">
-        <v>89</v>
-      </c>
-      <c r="B284">
-        <v>20402</v>
-      </c>
-      <c r="C284">
-        <v>3500</v>
-      </c>
+      <c r="A284" s="34"/>
+      <c r="B284" s="19"/>
+      <c r="C284" s="19"/>
       <c r="D284">
-        <v>1000</v>
-      </c>
-      <c r="E284" t="s">
-        <v>90</v>
+        <v>800</v>
+      </c>
+      <c r="E284" s="21" t="s">
+        <v>88</v>
       </c>
       <c r="F284" s="13">
-        <v>46049</v>
+        <v>46001</v>
       </c>
       <c r="G284">
-        <f>C284-D284</f>
-        <v>2500</v>
+        <f>G283-D284</f>
+        <v>0</v>
+      </c>
+      <c r="H284" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="I284"/>
       <c r="J284"/>
       <c r="K284"/>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A285" s="93"/>
-      <c r="D285">
-        <v>1966</v>
-      </c>
-      <c r="E285" t="s">
-        <v>91</v>
-      </c>
-      <c r="F285" s="13">
-        <v>46051</v>
-      </c>
-      <c r="G285">
-        <f>G284-D285</f>
-        <v>534</v>
-      </c>
-      <c r="H285" s="15"/>
+      <c r="A285" s="37"/>
+      <c r="B285" s="33"/>
+      <c r="C285" s="33"/>
+      <c r="D285" s="5"/>
+      <c r="E285" s="89"/>
+      <c r="F285" s="6"/>
+      <c r="G285" s="5"/>
+      <c r="H285" s="8"/>
       <c r="I285"/>
       <c r="J285"/>
       <c r="K285"/>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A286" s="93"/>
-      <c r="D286">
-        <v>534</v>
-      </c>
-      <c r="E286" t="s">
-        <v>92</v>
-      </c>
-      <c r="F286" s="13">
-        <v>46071</v>
-      </c>
-      <c r="G286">
-        <v>0</v>
-      </c>
+      <c r="A286" s="40"/>
+      <c r="B286" s="5"/>
+      <c r="C286" s="5"/>
+      <c r="D286" s="5"/>
+      <c r="E286" s="5"/>
+      <c r="F286" s="6"/>
+      <c r="G286" s="5"/>
+      <c r="H286" s="8"/>
       <c r="I286"/>
       <c r="J286"/>
       <c r="K286"/>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A287" s="93"/>
+      <c r="A287" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="B287">
+        <v>20402</v>
+      </c>
+      <c r="C287">
+        <v>3500</v>
+      </c>
       <c r="D287">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E287" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F287" s="13">
-        <v>46079</v>
+        <v>46049</v>
       </c>
       <c r="G287">
-        <f>G286-D287</f>
-        <v>-2000</v>
-      </c>
-      <c r="H287" s="15" t="s">
-        <v>11</v>
+        <f>C287-D287</f>
+        <v>2500</v>
       </c>
       <c r="I287"/>
       <c r="J287"/>
@@ -6624,18 +6633,18 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="93"/>
-      <c r="D288" s="17">
-        <v>1728</v>
-      </c>
-      <c r="E288" s="17" t="s">
-        <v>94</v>
+      <c r="D288">
+        <v>1966</v>
+      </c>
+      <c r="E288" t="s">
+        <v>91</v>
       </c>
       <c r="F288" s="13">
-        <v>46087</v>
+        <v>46051</v>
       </c>
       <c r="G288">
-        <f>G287+D288</f>
-        <v>-272</v>
+        <f>G287-D288</f>
+        <v>534</v>
       </c>
       <c r="H288" s="15"/>
       <c r="I288"/>
@@ -6644,83 +6653,80 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="93"/>
-      <c r="D289" s="17">
-        <v>272</v>
-      </c>
-      <c r="E289" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F289" s="13"/>
-      <c r="H289" s="15"/>
+      <c r="D289">
+        <v>534</v>
+      </c>
+      <c r="E289" t="s">
+        <v>92</v>
+      </c>
+      <c r="F289" s="13">
+        <v>46071</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
       <c r="I289"/>
       <c r="J289"/>
       <c r="K289"/>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A290" s="94"/>
-      <c r="B290" s="5"/>
-      <c r="C290" s="5"/>
-      <c r="D290" s="5"/>
-      <c r="E290" s="5"/>
-      <c r="F290" s="6"/>
-      <c r="G290" s="5"/>
-      <c r="H290" s="8"/>
+      <c r="A290" s="93"/>
+      <c r="D290">
+        <v>2000</v>
+      </c>
+      <c r="E290" t="s">
+        <v>93</v>
+      </c>
+      <c r="F290" s="13">
+        <v>46079</v>
+      </c>
+      <c r="G290">
+        <f>G289-D290</f>
+        <v>-2000</v>
+      </c>
+      <c r="H290" s="15" t="s">
+        <v>11</v>
+      </c>
       <c r="I290"/>
       <c r="J290"/>
       <c r="K290"/>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A291" s="93">
-        <v>46055</v>
-      </c>
-      <c r="B291">
-        <v>20542</v>
-      </c>
-      <c r="C291">
-        <v>3500</v>
-      </c>
-      <c r="D291">
-        <v>1400</v>
-      </c>
-      <c r="E291" t="s">
-        <v>96</v>
+      <c r="A291" s="93"/>
+      <c r="D291" s="17">
+        <v>1728</v>
+      </c>
+      <c r="E291" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="F291" s="13">
-        <v>46072</v>
+        <v>46087</v>
       </c>
       <c r="G291">
-        <f>C291-D291</f>
-        <v>2100</v>
-      </c>
-      <c r="H291" s="22"/>
+        <f>G290+D291</f>
+        <v>-272</v>
+      </c>
+      <c r="H291" s="15"/>
       <c r="I291"/>
       <c r="J291"/>
       <c r="K291"/>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="93"/>
-      <c r="D292">
-        <v>2100</v>
-      </c>
-      <c r="E292" t="s">
-        <v>97</v>
-      </c>
-      <c r="F292" s="13">
-        <v>46076</v>
-      </c>
-      <c r="G292">
-        <f>G291-D292</f>
-        <v>0</v>
-      </c>
-      <c r="H292" s="22" t="s">
-        <v>11</v>
-      </c>
+      <c r="D292" s="17">
+        <v>272</v>
+      </c>
+      <c r="E292" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F292" s="13"/>
+      <c r="H292" s="15"/>
       <c r="I292"/>
       <c r="J292"/>
       <c r="K292"/>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A293" s="40"/>
+      <c r="A293" s="94"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
       <c r="D293" s="5"/>
@@ -6733,246 +6739,253 @@
       <c r="K293"/>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A294" s="110"/>
-      <c r="B294" s="111"/>
-      <c r="F294" s="13"/>
-      <c r="H294" s="15"/>
+      <c r="A294" s="93">
+        <v>46055</v>
+      </c>
+      <c r="B294">
+        <v>20542</v>
+      </c>
+      <c r="C294">
+        <v>3500</v>
+      </c>
+      <c r="D294">
+        <v>1400</v>
+      </c>
+      <c r="E294" t="s">
+        <v>96</v>
+      </c>
+      <c r="F294" s="13">
+        <v>46072</v>
+      </c>
+      <c r="G294">
+        <f>C294-D294</f>
+        <v>2100</v>
+      </c>
+      <c r="H294" s="22"/>
       <c r="I294"/>
       <c r="J294"/>
       <c r="K294"/>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A295" s="110"/>
-      <c r="B295" s="111"/>
-      <c r="F295" s="13"/>
-      <c r="H295" s="15"/>
+      <c r="A295" s="93"/>
+      <c r="D295">
+        <v>2100</v>
+      </c>
+      <c r="E295" t="s">
+        <v>97</v>
+      </c>
+      <c r="F295" s="13">
+        <v>46076</v>
+      </c>
+      <c r="G295">
+        <f>G294-D295</f>
+        <v>0</v>
+      </c>
+      <c r="H295" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="I295"/>
       <c r="J295"/>
       <c r="K295"/>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A296" s="110"/>
-      <c r="B296" s="111"/>
-      <c r="F296" s="13"/>
-      <c r="H296" s="15"/>
+      <c r="A296" s="40"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="6"/>
+      <c r="G296" s="5"/>
+      <c r="H296" s="8"/>
       <c r="I296"/>
       <c r="J296"/>
       <c r="K296"/>
     </row>
-    <row r="297" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A297" s="24"/>
-      <c r="B297" s="25"/>
-      <c r="C297" s="25"/>
-      <c r="D297" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="E297" s="100"/>
-      <c r="F297" s="100"/>
-      <c r="G297" s="70">
-        <v>2000</v>
-      </c>
-      <c r="H297" s="28"/>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A297" s="133"/>
+      <c r="B297" s="117"/>
+      <c r="F297" s="13"/>
+      <c r="H297" s="15"/>
       <c r="I297"/>
       <c r="J297"/>
       <c r="K297"/>
     </row>
-    <row r="298" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A298" s="133"/>
+      <c r="B298" s="117"/>
+      <c r="F298" s="13"/>
+      <c r="H298" s="15"/>
       <c r="I298"/>
       <c r="J298"/>
       <c r="K298"/>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A299" s="101" t="s">
-        <v>98</v>
-      </c>
-      <c r="B299" s="102"/>
-      <c r="C299" s="102"/>
-      <c r="D299" s="102"/>
-      <c r="E299" s="102"/>
-      <c r="F299" s="102"/>
-      <c r="G299" s="102"/>
-      <c r="H299" s="103"/>
+      <c r="A299" s="133"/>
+      <c r="B299" s="117"/>
+      <c r="F299" s="13"/>
+      <c r="H299" s="15"/>
       <c r="I299"/>
       <c r="J299"/>
       <c r="K299"/>
     </row>
-    <row r="300" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A300" s="107"/>
-      <c r="B300" s="108"/>
-      <c r="C300" s="108"/>
-      <c r="D300" s="108"/>
-      <c r="E300" s="108"/>
-      <c r="F300" s="108"/>
-      <c r="G300" s="108"/>
-      <c r="H300" s="109"/>
+    <row r="300" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A300" s="24"/>
+      <c r="B300" s="25"/>
+      <c r="C300" s="25"/>
+      <c r="D300" s="112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E300" s="112"/>
+      <c r="F300" s="112"/>
+      <c r="G300" s="70">
+        <v>2000</v>
+      </c>
+      <c r="H300" s="28"/>
       <c r="I300"/>
       <c r="J300"/>
       <c r="K300"/>
     </row>
-    <row r="301" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A301" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F301" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G301" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H301" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="301" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I301"/>
       <c r="J301"/>
       <c r="K301"/>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A302" s="91">
-        <v>45975</v>
-      </c>
-      <c r="B302" s="92">
-        <v>19850</v>
-      </c>
-      <c r="C302" s="92">
-        <v>1500</v>
-      </c>
-      <c r="D302">
-        <v>1500</v>
-      </c>
-      <c r="E302" t="s">
-        <v>85</v>
-      </c>
-      <c r="F302" s="13">
-        <v>45995</v>
-      </c>
-      <c r="G302">
-        <f>C302-D302</f>
-        <v>0</v>
-      </c>
-      <c r="H302" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="A302" s="109" t="s">
+        <v>98</v>
+      </c>
+      <c r="B302" s="110"/>
+      <c r="C302" s="110"/>
+      <c r="D302" s="110"/>
+      <c r="E302" s="110"/>
+      <c r="F302" s="110"/>
+      <c r="G302" s="110"/>
+      <c r="H302" s="111"/>
       <c r="I302"/>
       <c r="J302"/>
       <c r="K302"/>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A303" s="32"/>
-      <c r="B303" s="33"/>
-      <c r="C303" s="33"/>
-      <c r="D303" s="5"/>
-      <c r="E303" s="5"/>
-      <c r="F303" s="6"/>
-      <c r="G303" s="5"/>
-      <c r="H303" s="8"/>
+    <row r="303" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A303" s="135"/>
+      <c r="B303" s="136"/>
+      <c r="C303" s="136"/>
+      <c r="D303" s="136"/>
+      <c r="E303" s="136"/>
+      <c r="F303" s="136"/>
+      <c r="G303" s="136"/>
+      <c r="H303" s="137"/>
       <c r="I303"/>
       <c r="J303"/>
       <c r="K303"/>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A304" s="34">
-        <v>45975</v>
-      </c>
-      <c r="B304" s="19">
-        <v>19851</v>
-      </c>
-      <c r="C304" s="19">
-        <v>1700</v>
-      </c>
-      <c r="D304">
-        <v>1700</v>
-      </c>
-      <c r="E304" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F304" s="13">
-        <v>46386</v>
-      </c>
-      <c r="G304">
-        <f>C304-D304</f>
-        <v>0</v>
-      </c>
-      <c r="H304" s="15" t="s">
-        <v>46</v>
+    <row r="304" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A304" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H304" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="I304"/>
       <c r="J304"/>
       <c r="K304"/>
     </row>
-    <row r="305" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="37"/>
-      <c r="B305" s="33"/>
-      <c r="C305" s="33"/>
-      <c r="D305" s="5"/>
-      <c r="E305" s="89"/>
-      <c r="F305" s="6"/>
-      <c r="G305" s="5"/>
-      <c r="H305" s="8"/>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A305" s="91">
+        <v>45975</v>
+      </c>
+      <c r="B305" s="92">
+        <v>19850</v>
+      </c>
+      <c r="C305" s="92">
+        <v>1500</v>
+      </c>
+      <c r="D305">
+        <v>1500</v>
+      </c>
+      <c r="E305" t="s">
+        <v>85</v>
+      </c>
+      <c r="F305" s="13">
+        <v>45995</v>
+      </c>
+      <c r="G305">
+        <f>C305-D305</f>
+        <v>0</v>
+      </c>
+      <c r="H305" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="I305"/>
       <c r="J305"/>
       <c r="K305"/>
     </row>
-    <row r="306" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="34">
-        <v>45975</v>
-      </c>
-      <c r="B306" s="19">
-        <v>19997</v>
-      </c>
-      <c r="C306" s="19">
-        <v>2000</v>
-      </c>
-      <c r="D306">
-        <v>2000</v>
-      </c>
-      <c r="E306" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F306" s="13">
-        <v>46001</v>
-      </c>
-      <c r="G306">
-        <f>C306-D306</f>
-        <v>0</v>
-      </c>
-      <c r="H306" s="15" t="s">
-        <v>29</v>
-      </c>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A306" s="32"/>
+      <c r="B306" s="33"/>
+      <c r="C306" s="33"/>
+      <c r="D306" s="5"/>
+      <c r="E306" s="5"/>
+      <c r="F306" s="6"/>
+      <c r="G306" s="5"/>
+      <c r="H306" s="8"/>
       <c r="I306"/>
       <c r="J306"/>
       <c r="K306"/>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A307" s="37"/>
-      <c r="B307" s="33"/>
-      <c r="C307" s="33"/>
-      <c r="D307" s="5"/>
-      <c r="E307" s="89"/>
-      <c r="F307" s="6"/>
-      <c r="G307" s="5"/>
-      <c r="H307" s="8"/>
+      <c r="A307" s="34">
+        <v>45975</v>
+      </c>
+      <c r="B307" s="19">
+        <v>19851</v>
+      </c>
+      <c r="C307" s="19">
+        <v>1700</v>
+      </c>
+      <c r="D307">
+        <v>1700</v>
+      </c>
+      <c r="E307" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F307" s="13">
+        <v>46386</v>
+      </c>
+      <c r="G307">
+        <f>C307-D307</f>
+        <v>0</v>
+      </c>
+      <c r="H307" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="I307"/>
       <c r="J307"/>
       <c r="K307"/>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A308" s="40"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="5"/>
+    <row r="308" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="37"/>
+      <c r="B308" s="33"/>
+      <c r="C308" s="33"/>
       <c r="D308" s="5"/>
-      <c r="E308" s="5"/>
+      <c r="E308" s="89"/>
       <c r="F308" s="6"/>
       <c r="G308" s="5"/>
       <c r="H308" s="8"/>
@@ -6980,87 +6993,84 @@
       <c r="J308"/>
       <c r="K308"/>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A309" s="93" t="s">
-        <v>89</v>
-      </c>
-      <c r="B309">
-        <v>20402</v>
-      </c>
-      <c r="C309">
-        <v>3500</v>
+    <row r="309" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="34">
+        <v>45975</v>
+      </c>
+      <c r="B309" s="19">
+        <v>19997</v>
+      </c>
+      <c r="C309" s="19">
+        <v>2000</v>
       </c>
       <c r="D309">
-        <v>200</v>
-      </c>
-      <c r="E309" t="s">
-        <v>99</v>
+        <v>2000</v>
+      </c>
+      <c r="E309" s="21" t="s">
+        <v>88</v>
       </c>
       <c r="F309" s="13">
-        <v>46049</v>
+        <v>46001</v>
       </c>
       <c r="G309">
         <f>C309-D309</f>
-        <v>3300</v>
-      </c>
-      <c r="H309" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="H309" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="I309"/>
       <c r="J309"/>
       <c r="K309"/>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A310" s="93"/>
-      <c r="D310">
-        <v>2600</v>
-      </c>
-      <c r="E310" t="s">
-        <v>91</v>
-      </c>
-      <c r="F310" s="13">
-        <v>46051</v>
-      </c>
-      <c r="G310">
-        <f>G309-D310</f>
-        <v>700</v>
-      </c>
-      <c r="H310" s="15"/>
+      <c r="A310" s="37"/>
+      <c r="B310" s="33"/>
+      <c r="C310" s="33"/>
+      <c r="D310" s="5"/>
+      <c r="E310" s="89"/>
+      <c r="F310" s="6"/>
+      <c r="G310" s="5"/>
+      <c r="H310" s="8"/>
       <c r="I310"/>
       <c r="J310"/>
       <c r="K310"/>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A311" s="93"/>
-      <c r="D311">
-        <v>515</v>
-      </c>
-      <c r="E311" t="s">
-        <v>100</v>
-      </c>
-      <c r="F311" s="13">
-        <v>46066</v>
-      </c>
-      <c r="G311">
-        <f>G310-D311</f>
-        <v>185</v>
-      </c>
-      <c r="H311" s="15"/>
+      <c r="A311" s="40"/>
+      <c r="B311" s="5"/>
+      <c r="C311" s="5"/>
+      <c r="D311" s="5"/>
+      <c r="E311" s="5"/>
+      <c r="F311" s="6"/>
+      <c r="G311" s="5"/>
+      <c r="H311" s="8"/>
       <c r="I311"/>
       <c r="J311"/>
       <c r="K311"/>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A312" s="93"/>
+      <c r="A312" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="B312">
+        <v>20402</v>
+      </c>
+      <c r="C312">
+        <v>3500</v>
+      </c>
       <c r="D312">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="E312" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F312" s="13">
-        <v>46071</v>
+        <v>46049</v>
       </c>
       <c r="G312">
-        <v>0</v>
+        <f>C312-D312</f>
+        <v>3300</v>
       </c>
       <c r="H312" s="15"/>
       <c r="I312"/>
@@ -7070,16 +7080,17 @@
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="93"/>
       <c r="D313">
-        <v>800</v>
+        <v>2600</v>
       </c>
       <c r="E313" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F313" s="13">
-        <v>46079</v>
+        <v>46051</v>
       </c>
       <c r="G313">
-        <v>800</v>
+        <f>G312-D313</f>
+        <v>700</v>
       </c>
       <c r="H313" s="15"/>
       <c r="I313"/>
@@ -7089,62 +7100,57 @@
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="93"/>
       <c r="D314">
-        <v>800</v>
+        <v>515</v>
       </c>
       <c r="E314" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F314" s="13">
-        <v>46087</v>
+        <v>46066</v>
       </c>
       <c r="G314">
         <f>G313-D314</f>
-        <v>0</v>
-      </c>
-      <c r="H314" s="15" t="s">
-        <v>11</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="H314" s="15"/>
       <c r="I314"/>
       <c r="J314"/>
       <c r="K314"/>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A315" s="94"/>
-      <c r="B315" s="5"/>
-      <c r="C315" s="5"/>
-      <c r="D315" s="5"/>
-      <c r="E315" s="5"/>
-      <c r="F315" s="6"/>
-      <c r="G315" s="5"/>
-      <c r="H315" s="8"/>
+      <c r="A315" s="93"/>
+      <c r="D315">
+        <v>185</v>
+      </c>
+      <c r="E315" t="s">
+        <v>92</v>
+      </c>
+      <c r="F315" s="13">
+        <v>46071</v>
+      </c>
+      <c r="G315">
+        <v>0</v>
+      </c>
+      <c r="H315" s="15"/>
       <c r="I315"/>
       <c r="J315"/>
       <c r="K315"/>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A316" s="93">
-        <v>46056</v>
-      </c>
-      <c r="B316">
-        <v>20542</v>
-      </c>
-      <c r="C316">
-        <v>3500</v>
-      </c>
+      <c r="A316" s="93"/>
       <c r="D316">
-        <v>2800</v>
+        <v>800</v>
       </c>
       <c r="E316" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F316" s="13">
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="G316">
-        <f>C316-D316</f>
-        <v>700</v>
-      </c>
-      <c r="H316" s="22"/>
+        <v>800</v>
+      </c>
+      <c r="H316" s="15"/>
       <c r="I316"/>
       <c r="J316"/>
       <c r="K316"/>
@@ -7152,19 +7158,19 @@
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="93"/>
       <c r="D317">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E317" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F317" s="13">
-        <v>46076</v>
+        <v>46087</v>
       </c>
       <c r="G317">
         <f>G316-D317</f>
         <v>0</v>
       </c>
-      <c r="H317" s="22" t="s">
+      <c r="H317" s="15" t="s">
         <v>11</v>
       </c>
       <c r="I317"/>
@@ -7172,7 +7178,7 @@
       <c r="K317"/>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A318" s="40"/>
+      <c r="A318" s="94"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
@@ -7185,184 +7191,186 @@
       <c r="K318"/>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A319" s="43"/>
+      <c r="A319" s="93">
+        <v>46056</v>
+      </c>
+      <c r="B319">
+        <v>20542</v>
+      </c>
+      <c r="C319">
+        <v>3500</v>
+      </c>
+      <c r="D319">
+        <v>2800</v>
+      </c>
       <c r="E319" t="s">
-        <v>104</v>
-      </c>
-      <c r="F319" s="13"/>
-      <c r="H319" s="15"/>
+        <v>102</v>
+      </c>
+      <c r="F319" s="13">
+        <v>46072</v>
+      </c>
+      <c r="G319">
+        <f>C319-D319</f>
+        <v>700</v>
+      </c>
+      <c r="H319" s="22"/>
       <c r="I319"/>
       <c r="J319"/>
       <c r="K319"/>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A320" s="43"/>
-      <c r="F320" s="13"/>
-      <c r="H320" s="15"/>
+      <c r="A320" s="93"/>
+      <c r="D320">
+        <v>700</v>
+      </c>
+      <c r="E320" t="s">
+        <v>103</v>
+      </c>
+      <c r="F320" s="13">
+        <v>46076</v>
+      </c>
+      <c r="G320">
+        <f>G319-D320</f>
+        <v>0</v>
+      </c>
+      <c r="H320" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="I320"/>
       <c r="J320"/>
       <c r="K320"/>
     </row>
-    <row r="321" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A321" s="24"/>
-      <c r="B321" s="25"/>
-      <c r="C321" s="25"/>
-      <c r="D321" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="E321" s="100"/>
-      <c r="F321" s="100"/>
-      <c r="G321" s="70">
-        <v>0</v>
-      </c>
-      <c r="H321" s="28"/>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A321" s="40"/>
+      <c r="B321" s="5"/>
+      <c r="C321" s="5"/>
+      <c r="D321" s="5"/>
+      <c r="E321" s="5"/>
+      <c r="F321" s="6"/>
+      <c r="G321" s="5"/>
+      <c r="H321" s="8"/>
       <c r="I321"/>
       <c r="J321"/>
       <c r="K321"/>
     </row>
-    <row r="322" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A322" s="43"/>
+      <c r="E322" t="s">
+        <v>104</v>
+      </c>
+      <c r="F322" s="13"/>
+      <c r="H322" s="15"/>
       <c r="I322"/>
       <c r="J322"/>
       <c r="K322"/>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A323" s="101" t="s">
-        <v>105</v>
-      </c>
-      <c r="B323" s="102"/>
-      <c r="C323" s="102"/>
-      <c r="D323" s="102"/>
-      <c r="E323" s="102"/>
-      <c r="F323" s="102"/>
-      <c r="G323" s="102"/>
-      <c r="H323" s="103"/>
+      <c r="A323" s="43"/>
+      <c r="F323" s="13"/>
+      <c r="H323" s="15"/>
       <c r="I323"/>
       <c r="J323"/>
       <c r="K323"/>
     </row>
-    <row r="324" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A324" s="104"/>
-      <c r="B324" s="105"/>
-      <c r="C324" s="105"/>
-      <c r="D324" s="105"/>
-      <c r="E324" s="105"/>
-      <c r="F324" s="105"/>
-      <c r="G324" s="105"/>
-      <c r="H324" s="106"/>
+    <row r="324" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A324" s="24"/>
+      <c r="B324" s="25"/>
+      <c r="C324" s="25"/>
+      <c r="D324" s="112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E324" s="112"/>
+      <c r="F324" s="112"/>
+      <c r="G324" s="70">
+        <v>0</v>
+      </c>
+      <c r="H324" s="28"/>
       <c r="I324"/>
       <c r="J324"/>
       <c r="K324"/>
     </row>
-    <row r="325" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A325" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E325" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F325" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G325" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H325" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="325" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I325"/>
       <c r="J325"/>
       <c r="K325"/>
     </row>
-    <row r="326" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="91">
-        <v>45975</v>
-      </c>
-      <c r="B326" s="92">
-        <v>19850</v>
-      </c>
-      <c r="C326" s="92">
-        <v>1500</v>
-      </c>
-      <c r="D326">
-        <v>600</v>
-      </c>
-      <c r="E326" t="s">
-        <v>106</v>
-      </c>
-      <c r="F326" s="13"/>
-      <c r="G326">
-        <f>C326-D326</f>
-        <v>900</v>
-      </c>
-      <c r="H326" s="15" t="s">
-        <v>29</v>
-      </c>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A326" s="109" t="s">
+        <v>105</v>
+      </c>
+      <c r="B326" s="110"/>
+      <c r="C326" s="110"/>
+      <c r="D326" s="110"/>
+      <c r="E326" s="110"/>
+      <c r="F326" s="110"/>
+      <c r="G326" s="110"/>
+      <c r="H326" s="111"/>
       <c r="I326"/>
       <c r="J326"/>
       <c r="K326"/>
     </row>
-    <row r="327" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="12"/>
-      <c r="D327">
-        <v>900</v>
-      </c>
-      <c r="E327" t="s">
-        <v>107</v>
-      </c>
-      <c r="F327" s="13"/>
-      <c r="G327">
-        <f>G326-D327</f>
-        <v>0</v>
-      </c>
-      <c r="H327" s="15"/>
+    <row r="327" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A327" s="123"/>
+      <c r="B327" s="124"/>
+      <c r="C327" s="124"/>
+      <c r="D327" s="124"/>
+      <c r="E327" s="124"/>
+      <c r="F327" s="124"/>
+      <c r="G327" s="124"/>
+      <c r="H327" s="125"/>
       <c r="I327"/>
       <c r="J327"/>
       <c r="K327"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A328" s="32"/>
-      <c r="B328" s="33"/>
-      <c r="C328" s="33"/>
-      <c r="D328" s="5"/>
-      <c r="E328" s="5"/>
-      <c r="F328" s="6"/>
-      <c r="G328" s="5"/>
-      <c r="H328" s="8"/>
+    <row r="328" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A328" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G328" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I328"/>
       <c r="J328"/>
       <c r="K328"/>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A329" s="34">
+    <row r="329" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A329" s="91">
         <v>45975</v>
       </c>
-      <c r="B329" s="19">
-        <v>19851</v>
-      </c>
-      <c r="C329" s="19">
+      <c r="B329" s="92">
+        <v>19850</v>
+      </c>
+      <c r="C329" s="92">
         <v>1500</v>
       </c>
       <c r="D329">
-        <v>1500</v>
-      </c>
-      <c r="E329" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F329" s="13">
-        <v>46386</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E329" t="s">
+        <v>106</v>
+      </c>
+      <c r="F329" s="13"/>
       <c r="G329">
         <f>C329-D329</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H329" s="15" t="s">
         <v>29</v>
@@ -7371,23 +7379,30 @@
       <c r="J329"/>
       <c r="K329"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A330" s="34"/>
-      <c r="B330" s="19"/>
-      <c r="C330" s="19"/>
-      <c r="E330" s="21"/>
+    <row r="330" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A330" s="12"/>
+      <c r="D330">
+        <v>900</v>
+      </c>
+      <c r="E330" t="s">
+        <v>107</v>
+      </c>
       <c r="F330" s="13"/>
+      <c r="G330">
+        <f>G329-D330</f>
+        <v>0</v>
+      </c>
       <c r="H330" s="15"/>
       <c r="I330"/>
       <c r="J330"/>
       <c r="K330"/>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A331" s="37"/>
+      <c r="A331" s="32"/>
       <c r="B331" s="33"/>
       <c r="C331" s="33"/>
       <c r="D331" s="5"/>
-      <c r="E331" s="89"/>
+      <c r="E331" s="5"/>
       <c r="F331" s="6"/>
       <c r="G331" s="5"/>
       <c r="H331" s="8"/>
@@ -7400,19 +7415,19 @@
         <v>45975</v>
       </c>
       <c r="B332" s="19">
-        <v>19997</v>
+        <v>19851</v>
       </c>
       <c r="C332" s="19">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D332">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F332" s="13">
-        <v>46001</v>
+        <v>46386</v>
       </c>
       <c r="G332">
         <f>C332-D332</f>
@@ -7450,85 +7465,81 @@
       <c r="K334"/>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A335" s="12">
-        <v>46041</v>
-      </c>
-      <c r="B335">
-        <v>20402</v>
-      </c>
-      <c r="C335">
-        <v>3000</v>
+      <c r="A335" s="34">
+        <v>45975</v>
+      </c>
+      <c r="B335" s="19">
+        <v>19997</v>
+      </c>
+      <c r="C335" s="19">
+        <v>2000</v>
       </c>
       <c r="D335">
-        <v>400</v>
-      </c>
-      <c r="E335" t="s">
-        <v>90</v>
+        <v>2000</v>
+      </c>
+      <c r="E335" s="21" t="s">
+        <v>88</v>
       </c>
       <c r="F335" s="13">
-        <v>46049</v>
+        <v>46001</v>
       </c>
       <c r="G335">
         <f>C335-D335</f>
-        <v>2600</v>
-      </c>
-      <c r="H335" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="H335" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="I335"/>
       <c r="J335"/>
       <c r="K335"/>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A336" s="12"/>
-      <c r="D336">
-        <v>2300</v>
-      </c>
-      <c r="E336" t="s">
-        <v>100</v>
-      </c>
-      <c r="F336" s="13">
-        <v>46066</v>
-      </c>
-      <c r="G336">
-        <f>G335-D336</f>
-        <v>300</v>
-      </c>
+      <c r="A336" s="34"/>
+      <c r="B336" s="19"/>
+      <c r="C336" s="19"/>
+      <c r="E336" s="21"/>
+      <c r="F336" s="13"/>
       <c r="H336" s="15"/>
       <c r="I336"/>
       <c r="J336"/>
       <c r="K336"/>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A337" s="12"/>
-      <c r="D337">
-        <v>300</v>
-      </c>
-      <c r="E337" t="s">
-        <v>92</v>
-      </c>
-      <c r="F337" s="13">
-        <v>46071</v>
-      </c>
-      <c r="G337">
-        <v>0</v>
-      </c>
-      <c r="H337" s="15"/>
+      <c r="A337" s="37"/>
+      <c r="B337" s="33"/>
+      <c r="C337" s="33"/>
+      <c r="D337" s="5"/>
+      <c r="E337" s="89"/>
+      <c r="F337" s="6"/>
+      <c r="G337" s="5"/>
+      <c r="H337" s="8"/>
       <c r="I337"/>
       <c r="J337"/>
       <c r="K337"/>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A338" s="12"/>
+      <c r="A338" s="12">
+        <v>46041</v>
+      </c>
+      <c r="B338">
+        <v>20402</v>
+      </c>
+      <c r="C338">
+        <v>3000</v>
+      </c>
       <c r="D338">
-        <v>2800</v>
+        <v>400</v>
       </c>
       <c r="E338" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F338" s="13">
-        <v>46079</v>
+        <v>46049</v>
       </c>
       <c r="G338">
-        <v>2800</v>
+        <f>C338-D338</f>
+        <v>2600</v>
       </c>
       <c r="H338" s="15"/>
       <c r="I338"/>
@@ -7537,149 +7548,192 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="12"/>
-      <c r="D339" s="17">
-        <v>2800</v>
-      </c>
-      <c r="E339" s="17" t="s">
-        <v>101</v>
+      <c r="D339">
+        <v>2300</v>
+      </c>
+      <c r="E339" t="s">
+        <v>100</v>
       </c>
       <c r="F339" s="13">
-        <v>46087</v>
+        <v>46066</v>
       </c>
       <c r="G339">
         <f>G338-D339</f>
-        <v>0</v>
-      </c>
-      <c r="H339" s="15" t="s">
-        <v>11</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H339" s="15"/>
       <c r="I339"/>
       <c r="J339"/>
       <c r="K339"/>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A340" s="95"/>
-      <c r="B340" s="96"/>
-      <c r="C340" s="96"/>
-      <c r="D340" s="96"/>
-      <c r="E340" s="96"/>
-      <c r="F340" s="97"/>
-      <c r="G340" s="96"/>
-      <c r="H340" s="36"/>
+      <c r="A340" s="12"/>
+      <c r="D340">
+        <v>300</v>
+      </c>
+      <c r="E340" t="s">
+        <v>92</v>
+      </c>
+      <c r="F340" s="13">
+        <v>46071</v>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340" s="15"/>
       <c r="I340"/>
       <c r="J340"/>
       <c r="K340"/>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A341" s="12">
-        <v>46056</v>
-      </c>
-      <c r="B341">
-        <v>20542</v>
-      </c>
-      <c r="C341">
-        <v>3000</v>
-      </c>
+      <c r="A341" s="12"/>
       <c r="D341">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="E341" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F341" s="13">
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="G341">
-        <f>C341-D341</f>
-        <v>1000</v>
-      </c>
-      <c r="H341" s="22"/>
+        <v>2800</v>
+      </c>
+      <c r="H341" s="15"/>
       <c r="I341"/>
       <c r="J341"/>
       <c r="K341"/>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="12"/>
-      <c r="D342">
-        <v>1000</v>
-      </c>
-      <c r="E342" t="s">
-        <v>108</v>
+      <c r="D342" s="17">
+        <v>2800</v>
+      </c>
+      <c r="E342" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="F342" s="13">
-        <v>46076</v>
+        <v>46087</v>
       </c>
       <c r="G342">
         <f>G341-D342</f>
         <v>0</v>
       </c>
-      <c r="H342" s="22"/>
+      <c r="H342" s="15" t="s">
+        <v>11</v>
+      </c>
       <c r="I342"/>
       <c r="J342"/>
       <c r="K342"/>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A343" s="12"/>
-      <c r="D343">
-        <v>500</v>
-      </c>
-      <c r="E343" t="s">
-        <v>109</v>
-      </c>
-      <c r="F343" s="13">
-        <v>46076</v>
-      </c>
-      <c r="G343">
-        <v>500</v>
-      </c>
-      <c r="H343" s="22" t="s">
-        <v>11</v>
-      </c>
+      <c r="A343" s="95"/>
+      <c r="B343" s="96"/>
+      <c r="C343" s="96"/>
+      <c r="D343" s="96"/>
+      <c r="E343" s="96"/>
+      <c r="F343" s="97"/>
+      <c r="G343" s="96"/>
+      <c r="H343" s="36"/>
       <c r="I343"/>
       <c r="J343"/>
       <c r="K343"/>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A344" s="40"/>
-      <c r="B344" s="5"/>
-      <c r="C344" s="5"/>
-      <c r="D344" s="5"/>
-      <c r="E344" s="5"/>
-      <c r="F344" s="5"/>
-      <c r="G344" s="5"/>
-      <c r="H344" s="98"/>
+      <c r="A344" s="12">
+        <v>46056</v>
+      </c>
+      <c r="B344">
+        <v>20542</v>
+      </c>
+      <c r="C344">
+        <v>3000</v>
+      </c>
+      <c r="D344">
+        <v>2000</v>
+      </c>
+      <c r="E344" t="s">
+        <v>102</v>
+      </c>
+      <c r="F344" s="13">
+        <v>46072</v>
+      </c>
+      <c r="G344">
+        <f>C344-D344</f>
+        <v>1000</v>
+      </c>
+      <c r="H344" s="22"/>
       <c r="I344"/>
       <c r="J344"/>
       <c r="K344"/>
     </row>
-    <row r="345" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A345" s="24"/>
-      <c r="B345" s="25"/>
-      <c r="C345" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="D345" s="100"/>
-      <c r="E345" s="100"/>
-      <c r="F345" s="100"/>
-      <c r="G345" s="70">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A345" s="12"/>
+      <c r="D345">
+        <v>1000</v>
+      </c>
+      <c r="E345" t="s">
+        <v>108</v>
+      </c>
+      <c r="F345" s="13">
+        <v>46076</v>
+      </c>
+      <c r="G345">
+        <f>G344-D345</f>
         <v>0</v>
       </c>
-      <c r="H345" s="99"/>
+      <c r="H345" s="22"/>
       <c r="I345"/>
       <c r="J345"/>
       <c r="K345"/>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A346" s="12"/>
+      <c r="D346">
+        <v>500</v>
+      </c>
+      <c r="E346" t="s">
+        <v>109</v>
+      </c>
+      <c r="F346" s="13">
+        <v>46076</v>
+      </c>
+      <c r="G346">
+        <v>500</v>
+      </c>
+      <c r="H346" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="I346"/>
       <c r="J346"/>
       <c r="K346"/>
     </row>
-    <row r="347" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A347" s="40"/>
+      <c r="B347" s="5"/>
+      <c r="C347" s="5"/>
+      <c r="D347" s="5"/>
+      <c r="E347" s="5"/>
+      <c r="F347" s="5"/>
+      <c r="G347" s="5"/>
+      <c r="H347" s="98"/>
       <c r="I347"/>
       <c r="J347"/>
       <c r="K347"/>
     </row>
-    <row r="348" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A348" s="24"/>
+      <c r="B348" s="25"/>
+      <c r="C348" s="112" t="s">
+        <v>16</v>
+      </c>
+      <c r="D348" s="112"/>
+      <c r="E348" s="112"/>
+      <c r="F348" s="112"/>
+      <c r="G348" s="70">
+        <v>0</v>
+      </c>
+      <c r="H348" s="99"/>
       <c r="I348"/>
       <c r="J348"/>
       <c r="K348"/>
@@ -7689,12 +7743,12 @@
       <c r="J349"/>
       <c r="K349"/>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I350"/>
       <c r="J350"/>
       <c r="K350"/>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I351"/>
       <c r="J351"/>
       <c r="K351"/>
@@ -7739,12 +7793,12 @@
       <c r="J359"/>
       <c r="K359"/>
     </row>
-    <row r="360" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I360"/>
       <c r="J360"/>
       <c r="K360"/>
     </row>
-    <row r="361" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I361"/>
       <c r="J361"/>
       <c r="K361"/>
@@ -7754,12 +7808,12 @@
       <c r="J362"/>
       <c r="K362"/>
     </row>
-    <row r="363" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I363"/>
       <c r="J363"/>
       <c r="K363"/>
     </row>
-    <row r="364" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I364"/>
       <c r="J364"/>
       <c r="K364"/>
@@ -7779,12 +7833,12 @@
       <c r="J367"/>
       <c r="K367"/>
     </row>
-    <row r="368" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I368"/>
       <c r="J368"/>
       <c r="K368"/>
     </row>
-    <row r="369" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I369"/>
       <c r="J369"/>
       <c r="K369"/>
@@ -7794,7 +7848,7 @@
       <c r="J370"/>
       <c r="K370"/>
     </row>
-    <row r="371" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I371"/>
       <c r="J371"/>
       <c r="K371"/>
@@ -7809,22 +7863,22 @@
       <c r="J373"/>
       <c r="K373"/>
     </row>
-    <row r="374" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I374"/>
       <c r="J374"/>
       <c r="K374"/>
     </row>
-    <row r="375" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I375"/>
       <c r="J375"/>
       <c r="K375"/>
     </row>
-    <row r="376" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I376"/>
       <c r="J376"/>
       <c r="K376"/>
     </row>
-    <row r="377" spans="9:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I377"/>
       <c r="J377"/>
       <c r="K377"/>
@@ -7834,12 +7888,12 @@
       <c r="J378"/>
       <c r="K378"/>
     </row>
-    <row r="379" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I379"/>
       <c r="J379"/>
       <c r="K379"/>
     </row>
-    <row r="380" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="9:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I380"/>
       <c r="J380"/>
       <c r="K380"/>
@@ -7864,12 +7918,12 @@
       <c r="J384"/>
       <c r="K384"/>
     </row>
-    <row r="385" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I385"/>
       <c r="J385"/>
       <c r="K385"/>
     </row>
-    <row r="386" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I386"/>
       <c r="J386"/>
       <c r="K386"/>
@@ -7879,12 +7933,12 @@
       <c r="J387"/>
       <c r="K387"/>
     </row>
-    <row r="388" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I388"/>
       <c r="J388"/>
       <c r="K388"/>
     </row>
-    <row r="389" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I389"/>
       <c r="J389"/>
       <c r="K389"/>
@@ -7899,12 +7953,12 @@
       <c r="J391"/>
       <c r="K391"/>
     </row>
-    <row r="392" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I392"/>
       <c r="J392"/>
       <c r="K392"/>
     </row>
-    <row r="393" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I393"/>
       <c r="J393"/>
       <c r="K393"/>
@@ -7914,12 +7968,12 @@
       <c r="J394"/>
       <c r="K394"/>
     </row>
-    <row r="395" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I395"/>
       <c r="J395"/>
       <c r="K395"/>
     </row>
-    <row r="396" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I396"/>
       <c r="J396"/>
       <c r="K396"/>
@@ -7934,12 +7988,12 @@
       <c r="J398"/>
       <c r="K398"/>
     </row>
-    <row r="399" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I399"/>
       <c r="J399"/>
       <c r="K399"/>
     </row>
-    <row r="400" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I400"/>
       <c r="J400"/>
       <c r="K400"/>
@@ -7949,12 +8003,12 @@
       <c r="J401"/>
       <c r="K401"/>
     </row>
-    <row r="402" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I402"/>
       <c r="J402"/>
       <c r="K402"/>
     </row>
-    <row r="403" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I403"/>
       <c r="J403"/>
       <c r="K403"/>
@@ -7979,12 +8033,12 @@
       <c r="J407"/>
       <c r="K407"/>
     </row>
-    <row r="408" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I408"/>
       <c r="J408"/>
       <c r="K408"/>
     </row>
-    <row r="409" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I409"/>
       <c r="J409"/>
       <c r="K409"/>
@@ -7994,12 +8048,12 @@
       <c r="J410"/>
       <c r="K410"/>
     </row>
-    <row r="411" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I411"/>
       <c r="J411"/>
       <c r="K411"/>
     </row>
-    <row r="412" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I412"/>
       <c r="J412"/>
       <c r="K412"/>
@@ -8059,12 +8113,12 @@
       <c r="J423"/>
       <c r="K423"/>
     </row>
-    <row r="424" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I424"/>
       <c r="J424"/>
       <c r="K424"/>
     </row>
-    <row r="425" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I425"/>
       <c r="J425"/>
       <c r="K425"/>
@@ -8074,12 +8128,12 @@
       <c r="J426"/>
       <c r="K426"/>
     </row>
-    <row r="427" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I427"/>
       <c r="J427"/>
       <c r="K427"/>
     </row>
-    <row r="428" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I428"/>
       <c r="J428"/>
       <c r="K428"/>
@@ -8179,12 +8233,12 @@
       <c r="J447"/>
       <c r="K447"/>
     </row>
-    <row r="448" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I448"/>
       <c r="J448"/>
       <c r="K448"/>
     </row>
-    <row r="449" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I449"/>
       <c r="J449"/>
       <c r="K449"/>
@@ -8194,12 +8248,12 @@
       <c r="J450"/>
       <c r="K450"/>
     </row>
-    <row r="451" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I451"/>
       <c r="J451"/>
       <c r="K451"/>
     </row>
-    <row r="452" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I452"/>
       <c r="J452"/>
       <c r="K452"/>
@@ -8359,12 +8413,12 @@
       <c r="J483"/>
       <c r="K483"/>
     </row>
-    <row r="484" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I484"/>
       <c r="J484"/>
       <c r="K484"/>
     </row>
-    <row r="485" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I485"/>
       <c r="J485"/>
       <c r="K485"/>
@@ -8374,12 +8428,12 @@
       <c r="J486"/>
       <c r="K486"/>
     </row>
-    <row r="487" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I487"/>
       <c r="J487"/>
       <c r="K487"/>
     </row>
-    <row r="488" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I488"/>
       <c r="J488"/>
       <c r="K488"/>
@@ -8494,12 +8548,12 @@
       <c r="J510"/>
       <c r="K510"/>
     </row>
-    <row r="511" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I511"/>
       <c r="J511"/>
       <c r="K511"/>
     </row>
-    <row r="512" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I512"/>
       <c r="J512"/>
       <c r="K512"/>
@@ -8509,12 +8563,12 @@
       <c r="J513"/>
       <c r="K513"/>
     </row>
-    <row r="514" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="9:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I514"/>
       <c r="J514"/>
       <c r="K514"/>
     </row>
-    <row r="515" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="9:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I515"/>
       <c r="J515"/>
       <c r="K515"/>
@@ -8529,7 +8583,7 @@
       <c r="J517"/>
       <c r="K517"/>
     </row>
-    <row r="518" spans="9:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I518"/>
       <c r="J518"/>
       <c r="K518"/>
@@ -8544,7 +8598,7 @@
       <c r="J520"/>
       <c r="K520"/>
     </row>
-    <row r="521" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="9:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I521"/>
       <c r="J521"/>
       <c r="K521"/>
@@ -8849,12 +8903,12 @@
       <c r="J581"/>
       <c r="K581"/>
     </row>
-    <row r="582" spans="9:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I582"/>
       <c r="J582"/>
       <c r="K582"/>
     </row>
-    <row r="583" spans="9:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="9:11" x14ac:dyDescent="0.3">
       <c r="I583"/>
       <c r="J583"/>
       <c r="K583"/>
@@ -8864,12 +8918,12 @@
       <c r="J584"/>
       <c r="K584"/>
     </row>
-    <row r="585" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="585" spans="9:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I585"/>
       <c r="J585"/>
       <c r="K585"/>
     </row>
-    <row r="586" spans="9:11" x14ac:dyDescent="0.3">
+    <row r="586" spans="9:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I586"/>
       <c r="J586"/>
       <c r="K586"/>
@@ -8959,52 +9013,62 @@
       <c r="J603"/>
       <c r="K603"/>
     </row>
-    <row r="604" spans="9:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L604" s="60"/>
-      <c r="M604" s="60"/>
-      <c r="N604" s="60"/>
-      <c r="O604" s="60"/>
-      <c r="P604" s="60"/>
-      <c r="R604" s="19"/>
-      <c r="S604" t="s">
+    <row r="604" spans="9:19" x14ac:dyDescent="0.3">
+      <c r="I604"/>
+      <c r="J604"/>
+      <c r="K604"/>
+    </row>
+    <row r="605" spans="9:19" x14ac:dyDescent="0.3">
+      <c r="I605"/>
+      <c r="J605"/>
+      <c r="K605"/>
+    </row>
+    <row r="606" spans="9:19" x14ac:dyDescent="0.3">
+      <c r="I606"/>
+      <c r="J606"/>
+      <c r="K606"/>
+    </row>
+    <row r="607" spans="9:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L607" s="60"/>
+      <c r="M607" s="60"/>
+      <c r="N607" s="60"/>
+      <c r="O607" s="60"/>
+      <c r="P607" s="60"/>
+      <c r="R607" s="19"/>
+      <c r="S607" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="605" spans="9:19" x14ac:dyDescent="0.3">
-      <c r="S605" t="s">
+    <row r="608" spans="9:19" x14ac:dyDescent="0.3">
+      <c r="S608" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="D321:F321"/>
-    <mergeCell ref="A323:H324"/>
-    <mergeCell ref="C345:F345"/>
-    <mergeCell ref="D269:F269"/>
-    <mergeCell ref="A271:H272"/>
-    <mergeCell ref="A294:A296"/>
-    <mergeCell ref="B294:B296"/>
-    <mergeCell ref="D297:F297"/>
-    <mergeCell ref="A299:H300"/>
-    <mergeCell ref="E220:F220"/>
-    <mergeCell ref="A222:H223"/>
-    <mergeCell ref="E241:F241"/>
-    <mergeCell ref="A243:H244"/>
-    <mergeCell ref="E255:F255"/>
-    <mergeCell ref="A257:H258"/>
+    <mergeCell ref="D324:F324"/>
+    <mergeCell ref="A326:H327"/>
+    <mergeCell ref="C348:F348"/>
+    <mergeCell ref="D272:F272"/>
+    <mergeCell ref="A274:H275"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="B297:B299"/>
+    <mergeCell ref="D300:F300"/>
+    <mergeCell ref="A302:H303"/>
+    <mergeCell ref="A260:H261"/>
     <mergeCell ref="A185:H186"/>
     <mergeCell ref="E192:F192"/>
     <mergeCell ref="A194:H195"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="A210:H211"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="B214:B216"/>
-    <mergeCell ref="C214:C216"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="A162:H163"/>
-    <mergeCell ref="A171:H172"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="A178:H179"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="B217:B219"/>
+    <mergeCell ref="C217:C219"/>
+    <mergeCell ref="E223:F223"/>
+    <mergeCell ref="A225:H226"/>
+    <mergeCell ref="E244:F244"/>
+    <mergeCell ref="A246:H247"/>
+    <mergeCell ref="E258:F258"/>
     <mergeCell ref="E183:F183"/>
     <mergeCell ref="A120:H121"/>
     <mergeCell ref="E131:F131"/>
@@ -9012,11 +9076,11 @@
     <mergeCell ref="E144:F144"/>
     <mergeCell ref="A146:H147"/>
     <mergeCell ref="A154:H155"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="A98:H99"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="A110:H111"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="A162:H163"/>
+    <mergeCell ref="A171:H172"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="A178:H179"/>
     <mergeCell ref="E118:F118"/>
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="E75:F75"/>
@@ -9024,11 +9088,11 @@
     <mergeCell ref="E86:F86"/>
     <mergeCell ref="A88:H89"/>
     <mergeCell ref="A91:H91"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A57:H58"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="A98:H99"/>
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="A110:H111"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E23:F23"/>
@@ -9036,6 +9100,11 @@
     <mergeCell ref="A30:A36"/>
     <mergeCell ref="B30:B36"/>
     <mergeCell ref="C30:C36"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A57:H58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
